--- a/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_oil_gas_integrated.xlsx
+++ b/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_oil_gas_integrated.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09376475024850342</v>
+        <v>0.0936132207480064</v>
       </c>
       <c r="C2">
-        <v>1879750.512789966</v>
+        <v>1864275.295018453</v>
       </c>
       <c r="D2">
-        <v>1816670.212789966</v>
+        <v>1820081.585018453</v>
       </c>
       <c r="E2">
-        <v>-80957.2</v>
+        <v>-62070.61</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>18886.59</v>
       </c>
       <c r="G2">
         <v>63080.3</v>
@@ -1457,28 +1457,28 @@
         <v>207730.1</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>949.9954769999999</v>
       </c>
       <c r="N2">
-        <v>207730.1</v>
+        <v>206780.104523</v>
       </c>
       <c r="O2">
-        <v>41546.02</v>
+        <v>41356.02090460001</v>
       </c>
       <c r="P2">
-        <v>166184.08</v>
+        <v>165424.0836184</v>
       </c>
       <c r="Q2">
-        <v>193181.58</v>
+        <v>192421.5836184</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09376475024850342</v>
+        <v>0.09415234418990547</v>
       </c>
       <c r="T2">
-        <v>0.9349222590860211</v>
+        <v>0.9424771864321708</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>218.6643042301559</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.0936132207480064</v>
+        <v>0.09346169124750939</v>
       </c>
       <c r="C3">
-        <v>1864275.295018453</v>
+        <v>1848812.913208604</v>
       </c>
       <c r="D3">
-        <v>1820081.585018453</v>
+        <v>1823505.793208604</v>
       </c>
       <c r="E3">
-        <v>-62070.61</v>
+        <v>-43184.02</v>
       </c>
       <c r="F3">
-        <v>18886.59</v>
+        <v>37773.18</v>
       </c>
       <c r="G3">
         <v>63080.3</v>
@@ -1539,28 +1539,28 @@
         <v>207730.1</v>
       </c>
       <c r="M3">
-        <v>949.9954769999999</v>
+        <v>1899.990954</v>
       </c>
       <c r="N3">
-        <v>206780.104523</v>
+        <v>205830.109046</v>
       </c>
       <c r="O3">
-        <v>41356.02090460001</v>
+        <v>41166.0218092</v>
       </c>
       <c r="P3">
-        <v>165424.0836184</v>
+        <v>164664.0872368</v>
       </c>
       <c r="Q3">
-        <v>192421.5836184</v>
+        <v>191661.5872368</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09415234418990547</v>
+        <v>0.09454784821174428</v>
       </c>
       <c r="T3">
-        <v>0.9424771864321708</v>
+        <v>0.9501862959690581</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>218.6643042301559</v>
+        <v>109.3321521150779</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09346169124750939</v>
+        <v>0.09331016174701239</v>
       </c>
       <c r="C4">
-        <v>1848812.913208604</v>
+        <v>1833363.439943733</v>
       </c>
       <c r="D4">
-        <v>1823505.793208604</v>
+        <v>1826942.909943733</v>
       </c>
       <c r="E4">
-        <v>-43184.02</v>
+        <v>-24297.43</v>
       </c>
       <c r="F4">
-        <v>37773.18</v>
+        <v>56659.77</v>
       </c>
       <c r="G4">
         <v>63080.3</v>
@@ -1621,28 +1621,28 @@
         <v>207730.1</v>
       </c>
       <c r="M4">
-        <v>1899.990954</v>
+        <v>2849.986431</v>
       </c>
       <c r="N4">
-        <v>205830.109046</v>
+        <v>204880.113569</v>
       </c>
       <c r="O4">
-        <v>41166.0218092</v>
+        <v>40976.0227138</v>
       </c>
       <c r="P4">
-        <v>164664.0872368</v>
+        <v>163904.0908552</v>
       </c>
       <c r="Q4">
-        <v>191661.5872368</v>
+        <v>190901.5908552</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09454784821174428</v>
+        <v>0.09495150695568287</v>
       </c>
       <c r="T4">
-        <v>0.9501862959690581</v>
+        <v>0.9580543562180462</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>109.3321521150779</v>
+        <v>72.88810141005195</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09331016174701239</v>
+        <v>0.0931586322465154</v>
       </c>
       <c r="C5">
-        <v>1833363.439943733</v>
+        <v>1817926.948355436</v>
       </c>
       <c r="D5">
-        <v>1826942.909943733</v>
+        <v>1830393.008355436</v>
       </c>
       <c r="E5">
-        <v>-24297.43</v>
+        <v>-5410.839999999997</v>
       </c>
       <c r="F5">
-        <v>56659.77</v>
+        <v>75546.36</v>
       </c>
       <c r="G5">
         <v>63080.3</v>
@@ -1703,28 +1703,28 @@
         <v>207730.1</v>
       </c>
       <c r="M5">
-        <v>2849.986431</v>
+        <v>3799.981908</v>
       </c>
       <c r="N5">
-        <v>204880.113569</v>
+        <v>203930.118092</v>
       </c>
       <c r="O5">
-        <v>40976.0227138</v>
+        <v>40786.02361840001</v>
       </c>
       <c r="P5">
-        <v>163904.0908552</v>
+        <v>163144.0944736</v>
       </c>
       <c r="Q5">
-        <v>190901.5908552</v>
+        <v>190141.5944736</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09495150695568287</v>
+        <v>0.09536357525678688</v>
       </c>
       <c r="T5">
-        <v>0.9580543562180462</v>
+        <v>0.9660863343888886</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>72.88810141005195</v>
+        <v>54.66607605753897</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.0931586322465154</v>
+        <v>0.09300710274601838</v>
       </c>
       <c r="C6">
-        <v>1817926.948355436</v>
+        <v>1802503.512128779</v>
       </c>
       <c r="D6">
-        <v>1830393.008355436</v>
+        <v>1833856.162128779</v>
       </c>
       <c r="E6">
-        <v>-5410.839999999997</v>
+        <v>13475.75000000001</v>
       </c>
       <c r="F6">
-        <v>75546.36</v>
+        <v>94432.95000000001</v>
       </c>
       <c r="G6">
         <v>63080.3</v>
@@ -1785,28 +1785,28 @@
         <v>207730.1</v>
       </c>
       <c r="M6">
-        <v>3799.981908</v>
+        <v>4749.977385</v>
       </c>
       <c r="N6">
-        <v>203930.118092</v>
+        <v>202980.122615</v>
       </c>
       <c r="O6">
-        <v>40786.02361840001</v>
+        <v>40596.024523</v>
       </c>
       <c r="P6">
-        <v>163144.0944736</v>
+        <v>162384.098092</v>
       </c>
       <c r="Q6">
-        <v>190141.5944736</v>
+        <v>189381.598092</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09536357525678688</v>
+        <v>0.09578431868001935</v>
       </c>
       <c r="T6">
-        <v>0.9660863343888886</v>
+        <v>0.9742874068370114</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>54.66607605753897</v>
+        <v>43.73286084603117</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09300710274601838</v>
+        <v>0.09285557324552136</v>
       </c>
       <c r="C7">
-        <v>1802503.512128779</v>
+        <v>1787093.205507539</v>
       </c>
       <c r="D7">
-        <v>1833856.162128779</v>
+        <v>1837332.445507539</v>
       </c>
       <c r="E7">
-        <v>13475.75000000001</v>
+        <v>32362.34000000001</v>
       </c>
       <c r="F7">
-        <v>94432.95000000001</v>
+        <v>113319.54</v>
       </c>
       <c r="G7">
         <v>63080.3</v>
@@ -1867,28 +1867,28 @@
         <v>207730.1</v>
       </c>
       <c r="M7">
-        <v>4749.977385</v>
+        <v>5699.972862000001</v>
       </c>
       <c r="N7">
-        <v>202980.122615</v>
+        <v>202030.127138</v>
       </c>
       <c r="O7">
-        <v>40596.024523</v>
+        <v>40406.02542760001</v>
       </c>
       <c r="P7">
-        <v>162384.098092</v>
+        <v>161624.1017104</v>
       </c>
       <c r="Q7">
-        <v>189381.598092</v>
+        <v>188621.6017104</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09578431868001935</v>
+        <v>0.09621401409098018</v>
       </c>
       <c r="T7">
-        <v>0.9742874068370114</v>
+        <v>0.9826629701882861</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>43.73286084603117</v>
+        <v>36.44405070502597</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09285557324552136</v>
+        <v>0.09270404374502438</v>
       </c>
       <c r="C8">
-        <v>1787093.205507539</v>
+        <v>1771696.103299513</v>
       </c>
       <c r="D8">
-        <v>1837332.445507539</v>
+        <v>1840821.933299513</v>
       </c>
       <c r="E8">
-        <v>32362.34</v>
+        <v>51248.92999999998</v>
       </c>
       <c r="F8">
-        <v>113319.54</v>
+        <v>132206.13</v>
       </c>
       <c r="G8">
         <v>63080.3</v>
@@ -1949,28 +1949,28 @@
         <v>207730.1</v>
       </c>
       <c r="M8">
-        <v>5699.972862</v>
+        <v>6649.968338999998</v>
       </c>
       <c r="N8">
-        <v>202030.127138</v>
+        <v>201080.131661</v>
       </c>
       <c r="O8">
-        <v>40406.02542760001</v>
+        <v>40216.02633220001</v>
       </c>
       <c r="P8">
-        <v>161624.1017104</v>
+        <v>160864.1053288</v>
       </c>
       <c r="Q8">
-        <v>188621.6017104</v>
+        <v>187861.6053288</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09621401409098018</v>
+        <v>0.09665295026346707</v>
       </c>
       <c r="T8">
-        <v>0.9826629701882861</v>
+        <v>0.9912186531815236</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>36.44405070502597</v>
+        <v>31.23775774716513</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09270404374502436</v>
+        <v>0.09255251424452737</v>
       </c>
       <c r="C9">
-        <v>1771696.103299514</v>
+        <v>1756312.280881886</v>
       </c>
       <c r="D9">
-        <v>1840821.933299514</v>
+        <v>1844324.700881886</v>
       </c>
       <c r="E9">
-        <v>51248.93000000001</v>
+        <v>70135.52</v>
       </c>
       <c r="F9">
-        <v>132206.13</v>
+        <v>151092.72</v>
       </c>
       <c r="G9">
         <v>63080.3</v>
@@ -2031,28 +2031,28 @@
         <v>207730.1</v>
       </c>
       <c r="M9">
-        <v>6649.968339</v>
+        <v>7599.963815999999</v>
       </c>
       <c r="N9">
-        <v>201080.131661</v>
+        <v>200130.136184</v>
       </c>
       <c r="O9">
-        <v>40216.0263322</v>
+        <v>40026.0272368</v>
       </c>
       <c r="P9">
-        <v>160864.1053288</v>
+        <v>160104.1089472</v>
       </c>
       <c r="Q9">
-        <v>187861.6053288</v>
+        <v>187101.6089472</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09665295026346707</v>
+        <v>0.09710142852666018</v>
       </c>
       <c r="T9">
-        <v>0.9912186531815236</v>
+        <v>0.9999603292833096</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>31.23775774716512</v>
+        <v>27.33303802876948</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09255251424452737</v>
+        <v>0.09240098474403036</v>
       </c>
       <c r="C10">
-        <v>1756312.280881886</v>
+        <v>1740941.814206651</v>
       </c>
       <c r="D10">
-        <v>1844324.700881886</v>
+        <v>1847840.824206651</v>
       </c>
       <c r="E10">
-        <v>70135.52</v>
+        <v>89022.11</v>
       </c>
       <c r="F10">
-        <v>151092.72</v>
+        <v>169979.31</v>
       </c>
       <c r="G10">
         <v>63080.3</v>
@@ -2113,28 +2113,28 @@
         <v>207730.1</v>
       </c>
       <c r="M10">
-        <v>7599.963815999999</v>
+        <v>8549.959293</v>
       </c>
       <c r="N10">
-        <v>200130.136184</v>
+        <v>199180.140707</v>
       </c>
       <c r="O10">
-        <v>40026.0272368</v>
+        <v>39836.02814140001</v>
       </c>
       <c r="P10">
-        <v>160104.1089472</v>
+        <v>159344.1125656</v>
       </c>
       <c r="Q10">
-        <v>187101.6089472</v>
+        <v>186341.6125656</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09710142852666018</v>
+        <v>0.09755976345497841</v>
       </c>
       <c r="T10">
-        <v>0.9999603292833096</v>
+        <v>1.008894130134585</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>27.33303802876948</v>
+        <v>24.29603380335065</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09240098474403036</v>
+        <v>0.09224945524353334</v>
       </c>
       <c r="C11">
-        <v>1740941.814206651</v>
+        <v>1725584.77980611</v>
       </c>
       <c r="D11">
-        <v>1847840.824206651</v>
+        <v>1851370.37980611</v>
       </c>
       <c r="E11">
-        <v>89022.11</v>
+        <v>107908.7</v>
       </c>
       <c r="F11">
-        <v>169979.31</v>
+        <v>188865.9</v>
       </c>
       <c r="G11">
         <v>63080.3</v>
@@ -2195,28 +2195,28 @@
         <v>207730.1</v>
       </c>
       <c r="M11">
-        <v>8549.959293</v>
+        <v>9499.954769999998</v>
       </c>
       <c r="N11">
-        <v>199180.140707</v>
+        <v>198230.14523</v>
       </c>
       <c r="O11">
-        <v>39836.02814140001</v>
+        <v>39646.029046</v>
       </c>
       <c r="P11">
-        <v>159344.1125656</v>
+        <v>158584.116184</v>
       </c>
       <c r="Q11">
-        <v>186341.6125656</v>
+        <v>185581.616184</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09755976345497841</v>
+        <v>0.09802828360392593</v>
       </c>
       <c r="T11">
-        <v>1.008894130134585</v>
+        <v>1.018026459893667</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>24.29603380335065</v>
+        <v>21.86643042301559</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09224945524353335</v>
+        <v>0.09209792574303634</v>
       </c>
       <c r="C12">
-        <v>1725584.77980611</v>
+        <v>1710241.254798415</v>
       </c>
       <c r="D12">
-        <v>1851370.37980611</v>
+        <v>1854913.444798415</v>
       </c>
       <c r="E12">
-        <v>107908.7</v>
+        <v>126795.29</v>
       </c>
       <c r="F12">
-        <v>188865.9</v>
+        <v>207752.49</v>
       </c>
       <c r="G12">
         <v>63080.3</v>
@@ -2277,28 +2277,28 @@
         <v>207730.1</v>
       </c>
       <c r="M12">
-        <v>9499.95477</v>
+        <v>10449.950247</v>
       </c>
       <c r="N12">
-        <v>198230.14523</v>
+        <v>197280.149753</v>
       </c>
       <c r="O12">
-        <v>39646.029046</v>
+        <v>39456.0299506</v>
       </c>
       <c r="P12">
-        <v>158584.116184</v>
+        <v>157824.1198024</v>
       </c>
       <c r="Q12">
-        <v>185581.616184</v>
+        <v>184821.6198024</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09802828360392594</v>
+        <v>0.09850733229554645</v>
       </c>
       <c r="T12">
-        <v>1.018026459893667</v>
+        <v>1.027364010546212</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>21.86643042301558</v>
+        <v>19.87857311183235</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09209792574303634</v>
+        <v>0.09194639624253934</v>
       </c>
       <c r="C13">
-        <v>1710241.254798415</v>
+        <v>1694911.316893194</v>
       </c>
       <c r="D13">
-        <v>1854913.444798415</v>
+        <v>1858470.096893194</v>
       </c>
       <c r="E13">
-        <v>126795.29</v>
+        <v>145681.88</v>
       </c>
       <c r="F13">
-        <v>207752.49</v>
+        <v>226639.08</v>
       </c>
       <c r="G13">
         <v>63080.3</v>
@@ -2359,28 +2359,28 @@
         <v>207730.1</v>
       </c>
       <c r="M13">
-        <v>10449.950247</v>
+        <v>11399.945724</v>
       </c>
       <c r="N13">
-        <v>197280.149753</v>
+        <v>196330.154276</v>
       </c>
       <c r="O13">
-        <v>39456.0299506</v>
+        <v>39266.03085520001</v>
       </c>
       <c r="P13">
-        <v>157824.1198024</v>
+        <v>157064.1234208</v>
       </c>
       <c r="Q13">
-        <v>184821.6198024</v>
+        <v>184061.6234208</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09850733229554645</v>
+        <v>0.09899726845743106</v>
       </c>
       <c r="T13">
-        <v>1.027364010546212</v>
+        <v>1.036913778259042</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>19.87857311183235</v>
+        <v>18.22202535251299</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09194639624253934</v>
+        <v>0.09179486674204233</v>
       </c>
       <c r="C14">
-        <v>1694911.316893194</v>
+        <v>1679595.044397225</v>
       </c>
       <c r="D14">
-        <v>1858470.096893194</v>
+        <v>1862040.414397225</v>
       </c>
       <c r="E14">
-        <v>145681.88</v>
+        <v>164568.47</v>
       </c>
       <c r="F14">
-        <v>226639.08</v>
+        <v>245525.67</v>
       </c>
       <c r="G14">
         <v>63080.3</v>
@@ -2441,28 +2441,28 @@
         <v>207730.1</v>
       </c>
       <c r="M14">
-        <v>11399.945724</v>
+        <v>12349.941201</v>
       </c>
       <c r="N14">
-        <v>196330.154276</v>
+        <v>195380.158799</v>
       </c>
       <c r="O14">
-        <v>39266.03085520001</v>
+        <v>39076.0317598</v>
       </c>
       <c r="P14">
-        <v>157064.1234208</v>
+        <v>156304.1270392</v>
       </c>
       <c r="Q14">
-        <v>184061.6234208</v>
+        <v>183301.6270392</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09899726845743106</v>
+        <v>0.09949846751958888</v>
       </c>
       <c r="T14">
-        <v>1.036913778259042</v>
+        <v>1.046683080861821</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>18.22202535251299</v>
+        <v>16.82033109462737</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09179486674204233</v>
+        <v>0.09164333724154532</v>
       </c>
       <c r="C15">
-        <v>1679595.044397225</v>
+        <v>1664292.516220192</v>
       </c>
       <c r="D15">
-        <v>1862040.414397225</v>
+        <v>1865624.476220192</v>
       </c>
       <c r="E15">
-        <v>164568.47</v>
+        <v>183455.06</v>
       </c>
       <c r="F15">
-        <v>245525.67</v>
+        <v>264412.26</v>
       </c>
       <c r="G15">
         <v>63080.3</v>
@@ -2523,28 +2523,28 @@
         <v>207730.1</v>
       </c>
       <c r="M15">
-        <v>12349.941201</v>
+        <v>13299.936678</v>
       </c>
       <c r="N15">
-        <v>195380.158799</v>
+        <v>194430.163322</v>
       </c>
       <c r="O15">
-        <v>39076.0317598</v>
+        <v>38886.0326644</v>
       </c>
       <c r="P15">
-        <v>156304.1270392</v>
+        <v>155544.1306576</v>
       </c>
       <c r="Q15">
-        <v>183301.6270392</v>
+        <v>182541.6306576</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09949846751958888</v>
+        <v>0.1000113223738899</v>
       </c>
       <c r="T15">
-        <v>1.046683080861821</v>
+        <v>1.056679576548387</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>16.82033109462737</v>
+        <v>15.61887887358256</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09164333724154532</v>
+        <v>0.0914918077410483</v>
       </c>
       <c r="C16">
-        <v>1664292.516220192</v>
+        <v>1649003.811880488</v>
       </c>
       <c r="D16">
-        <v>1865624.476220192</v>
+        <v>1869222.361880488</v>
       </c>
       <c r="E16">
-        <v>183455.06</v>
+        <v>202341.65</v>
       </c>
       <c r="F16">
-        <v>264412.26</v>
+        <v>283298.85</v>
       </c>
       <c r="G16">
         <v>63080.3</v>
@@ -2605,28 +2605,28 @@
         <v>207730.1</v>
       </c>
       <c r="M16">
-        <v>13299.936678</v>
+        <v>14249.932155</v>
       </c>
       <c r="N16">
-        <v>194430.163322</v>
+        <v>193480.167845</v>
       </c>
       <c r="O16">
-        <v>38886.0326644</v>
+        <v>38696.03356900001</v>
       </c>
       <c r="P16">
-        <v>155544.1306576</v>
+        <v>154784.134276</v>
       </c>
       <c r="Q16">
-        <v>182541.6306576</v>
+        <v>181781.634276</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1000113223738899</v>
+        <v>0.1005362444012333</v>
       </c>
       <c r="T16">
-        <v>1.056679576548387</v>
+        <v>1.066911283898165</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>15.61887887358256</v>
+        <v>14.57762028201039</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.0914918077410483</v>
+        <v>0.0913402782405513</v>
       </c>
       <c r="C17">
-        <v>1649003.811880488</v>
+        <v>1633729.011511103</v>
       </c>
       <c r="D17">
-        <v>1869222.361880488</v>
+        <v>1872834.151511103</v>
       </c>
       <c r="E17">
-        <v>202341.65</v>
+        <v>221228.24</v>
       </c>
       <c r="F17">
-        <v>283298.85</v>
+        <v>302185.44</v>
       </c>
       <c r="G17">
         <v>63080.3</v>
@@ -2687,28 +2687,28 @@
         <v>207730.1</v>
       </c>
       <c r="M17">
-        <v>14249.932155</v>
+        <v>15199.927632</v>
       </c>
       <c r="N17">
-        <v>193480.167845</v>
+        <v>192530.172368</v>
       </c>
       <c r="O17">
-        <v>38696.03356900001</v>
+        <v>38506.0344736</v>
       </c>
       <c r="P17">
-        <v>154784.134276</v>
+        <v>154024.1378944</v>
       </c>
       <c r="Q17">
-        <v>181781.634276</v>
+        <v>181021.6378944</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1005362444012333</v>
+        <v>0.1010736645720849</v>
       </c>
       <c r="T17">
-        <v>1.066911283898165</v>
+        <v>1.0773866033277</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>14.57762028201039</v>
+        <v>13.66651901438474</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.0913402782405513</v>
+        <v>0.09118874874005428</v>
       </c>
       <c r="C18">
-        <v>1633729.011511103</v>
+        <v>1618468.195865572</v>
       </c>
       <c r="D18">
-        <v>1872834.151511103</v>
+        <v>1876459.925865572</v>
       </c>
       <c r="E18">
-        <v>221228.24</v>
+        <v>240114.83</v>
       </c>
       <c r="F18">
-        <v>302185.44</v>
+        <v>321072.03</v>
       </c>
       <c r="G18">
         <v>63080.3</v>
@@ -2769,28 +2769,28 @@
         <v>207730.1</v>
       </c>
       <c r="M18">
-        <v>15199.927632</v>
+        <v>16149.923109</v>
       </c>
       <c r="N18">
-        <v>192530.172368</v>
+        <v>191580.176891</v>
       </c>
       <c r="O18">
-        <v>38506.0344736</v>
+        <v>38316.0353782</v>
       </c>
       <c r="P18">
-        <v>154024.1378944</v>
+        <v>153264.1415128</v>
       </c>
       <c r="Q18">
-        <v>181021.6378944</v>
+        <v>180261.6415128</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1010736645720849</v>
+        <v>0.1016240346265714</v>
       </c>
       <c r="T18">
-        <v>1.0773866033277</v>
+        <v>1.088114340092887</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>13.66651901438474</v>
+        <v>12.86260613118564</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09118874874005428</v>
+        <v>0.09103721923955731</v>
       </c>
       <c r="C19">
-        <v>1618468.195865572</v>
+        <v>1603221.446323991</v>
       </c>
       <c r="D19">
-        <v>1876459.925865572</v>
+        <v>1880099.766323991</v>
       </c>
       <c r="E19">
-        <v>240114.83</v>
+        <v>259001.42</v>
       </c>
       <c r="F19">
-        <v>321072.03</v>
+        <v>339958.6200000001</v>
       </c>
       <c r="G19">
         <v>63080.3</v>
@@ -2851,28 +2851,28 @@
         <v>207730.1</v>
       </c>
       <c r="M19">
-        <v>16149.923109</v>
+        <v>17099.918586</v>
       </c>
       <c r="N19">
-        <v>191580.176891</v>
+        <v>190630.181414</v>
       </c>
       <c r="O19">
-        <v>38316.0353782</v>
+        <v>38126.0362828</v>
       </c>
       <c r="P19">
-        <v>153264.1415128</v>
+        <v>152504.1451312</v>
       </c>
       <c r="Q19">
-        <v>180261.6415128</v>
+        <v>179501.6451312</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1016240346265714</v>
+        <v>0.1021878283409235</v>
       </c>
       <c r="T19">
-        <v>1.088114340092887</v>
+        <v>1.099103728974298</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>12.86260613118564</v>
+        <v>12.14801690167532</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09103721923955729</v>
+        <v>0.0908856897390603</v>
       </c>
       <c r="C20">
-        <v>1603221.446323991</v>
+        <v>1587988.84489911</v>
       </c>
       <c r="D20">
-        <v>1880099.766323991</v>
+        <v>1883753.75489911</v>
       </c>
       <c r="E20">
-        <v>259001.42</v>
+        <v>277888.01</v>
       </c>
       <c r="F20">
-        <v>339958.62</v>
+        <v>358845.21</v>
       </c>
       <c r="G20">
         <v>63080.3</v>
@@ -2933,28 +2933,28 @@
         <v>207730.1</v>
       </c>
       <c r="M20">
-        <v>17099.918586</v>
+        <v>18049.914063</v>
       </c>
       <c r="N20">
-        <v>190630.181414</v>
+        <v>189680.185937</v>
       </c>
       <c r="O20">
-        <v>38126.0362828</v>
+        <v>37936.0371874</v>
       </c>
       <c r="P20">
-        <v>152504.1451312</v>
+        <v>151744.1487496</v>
       </c>
       <c r="Q20">
-        <v>179501.6451312</v>
+        <v>178741.6487496</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1021878283409235</v>
+        <v>0.1027655428877288</v>
       </c>
       <c r="T20">
-        <v>1.099103728974298</v>
+        <v>1.110364460791052</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>12.14801690167532</v>
+        <v>11.50864759106083</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.0908856897390603</v>
+        <v>0.09073416023856329</v>
       </c>
       <c r="C21">
-        <v>1587988.84489911</v>
+        <v>1572770.474242489</v>
       </c>
       <c r="D21">
-        <v>1883753.75489911</v>
+        <v>1887421.974242489</v>
       </c>
       <c r="E21">
-        <v>277888.01</v>
+        <v>296774.6</v>
       </c>
       <c r="F21">
-        <v>358845.21</v>
+        <v>377731.8</v>
       </c>
       <c r="G21">
         <v>63080.3</v>
@@ -3015,28 +3015,28 @@
         <v>207730.1</v>
       </c>
       <c r="M21">
-        <v>18049.914063</v>
+        <v>18999.90954</v>
       </c>
       <c r="N21">
-        <v>189680.185937</v>
+        <v>188730.19046</v>
       </c>
       <c r="O21">
-        <v>37936.0371874</v>
+        <v>37746.038092</v>
       </c>
       <c r="P21">
-        <v>151744.1487496</v>
+        <v>150984.152368</v>
       </c>
       <c r="Q21">
-        <v>178741.6487496</v>
+        <v>177981.652368</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1027655428877288</v>
+        <v>0.1033577002982041</v>
       </c>
       <c r="T21">
-        <v>1.110364460791052</v>
+        <v>1.121906710903225</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>11.50864759106083</v>
+        <v>10.93321521150779</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09073416023856329</v>
+        <v>0.09058263073806629</v>
       </c>
       <c r="C22">
-        <v>1572770.474242489</v>
+        <v>1557566.41765073</v>
       </c>
       <c r="D22">
-        <v>1887421.974242489</v>
+        <v>1891104.50765073</v>
       </c>
       <c r="E22">
-        <v>296774.6</v>
+        <v>315661.19</v>
       </c>
       <c r="F22">
-        <v>377731.8</v>
+        <v>396618.39</v>
       </c>
       <c r="G22">
         <v>63080.3</v>
@@ -3097,28 +3097,28 @@
         <v>207730.1</v>
       </c>
       <c r="M22">
-        <v>18999.90954</v>
+        <v>19949.905017</v>
       </c>
       <c r="N22">
-        <v>188730.19046</v>
+        <v>187780.194983</v>
       </c>
       <c r="O22">
-        <v>37746.038092</v>
+        <v>37556.0389966</v>
       </c>
       <c r="P22">
-        <v>150984.152368</v>
+        <v>150224.1559864</v>
       </c>
       <c r="Q22">
-        <v>177981.652368</v>
+        <v>177221.6559864</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1033577002982041</v>
+        <v>0.1039648490355269</v>
       </c>
       <c r="T22">
-        <v>1.121906710903225</v>
+        <v>1.133741169878998</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>10.93321521150779</v>
+        <v>10.4125859157217</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09058263073806629</v>
+        <v>0.09043110123756926</v>
       </c>
       <c r="C23">
-        <v>1557566.41765073</v>
+        <v>1542376.759071784</v>
       </c>
       <c r="D23">
-        <v>1891104.50765073</v>
+        <v>1894801.439071784</v>
       </c>
       <c r="E23">
-        <v>315661.19</v>
+        <v>334547.78</v>
       </c>
       <c r="F23">
-        <v>396618.39</v>
+        <v>415504.98</v>
       </c>
       <c r="G23">
         <v>63080.3</v>
@@ -3179,28 +3179,28 @@
         <v>207730.1</v>
       </c>
       <c r="M23">
-        <v>19949.905017</v>
+        <v>20899.900494</v>
       </c>
       <c r="N23">
-        <v>187780.194983</v>
+        <v>186830.199506</v>
       </c>
       <c r="O23">
-        <v>37556.0389966</v>
+        <v>37366.03990120001</v>
       </c>
       <c r="P23">
-        <v>150224.1559864</v>
+        <v>149464.1596048</v>
       </c>
       <c r="Q23">
-        <v>177221.6559864</v>
+        <v>176461.6596048</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1039648490355269</v>
+        <v>0.1045875656891914</v>
       </c>
       <c r="T23">
-        <v>1.133741169878998</v>
+        <v>1.145879076520816</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>10.4125859157217</v>
+        <v>9.939286555916174</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09043110123756926</v>
+        <v>0.09027957173707227</v>
       </c>
       <c r="C24">
-        <v>1542376.759071784</v>
+        <v>1527201.583111329</v>
       </c>
       <c r="D24">
-        <v>1894801.439071784</v>
+        <v>1898512.853111329</v>
       </c>
       <c r="E24">
-        <v>334547.78</v>
+        <v>353434.37</v>
       </c>
       <c r="F24">
-        <v>415504.98</v>
+        <v>434391.57</v>
       </c>
       <c r="G24">
         <v>63080.3</v>
@@ -3261,28 +3261,28 @@
         <v>207730.1</v>
       </c>
       <c r="M24">
-        <v>20899.900494</v>
+        <v>21849.895971</v>
       </c>
       <c r="N24">
-        <v>186830.199506</v>
+        <v>185880.204029</v>
       </c>
       <c r="O24">
-        <v>37366.03990120001</v>
+        <v>37176.0408058</v>
       </c>
       <c r="P24">
-        <v>149464.1596048</v>
+        <v>148704.1632232</v>
       </c>
       <c r="Q24">
-        <v>176461.6596048</v>
+        <v>175701.6632232</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1045875656891914</v>
+        <v>0.1052264568013925</v>
       </c>
       <c r="T24">
-        <v>1.145879076520816</v>
+        <v>1.158332253465018</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>9.939286555916174</v>
+        <v>9.50714366218069</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09027957173707227</v>
+        <v>0.09012804223657526</v>
       </c>
       <c r="C25">
-        <v>1527201.583111329</v>
+        <v>1512040.975039225</v>
       </c>
       <c r="D25">
-        <v>1898512.853111329</v>
+        <v>1902238.835039224</v>
       </c>
       <c r="E25">
-        <v>353434.37</v>
+        <v>372320.96</v>
       </c>
       <c r="F25">
-        <v>434391.57</v>
+        <v>453278.16</v>
       </c>
       <c r="G25">
         <v>63080.3</v>
@@ -3343,28 +3343,28 @@
         <v>207730.1</v>
       </c>
       <c r="M25">
-        <v>21849.895971</v>
+        <v>22799.891448</v>
       </c>
       <c r="N25">
-        <v>185880.204029</v>
+        <v>184930.208552</v>
       </c>
       <c r="O25">
-        <v>37176.0408058</v>
+        <v>36986.0417104</v>
       </c>
       <c r="P25">
-        <v>148704.1632232</v>
+        <v>147944.1668416</v>
       </c>
       <c r="Q25">
-        <v>175701.6632232</v>
+        <v>174941.6668416</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1052264568013925</v>
+        <v>0.105882160837599</v>
       </c>
       <c r="T25">
-        <v>1.158332253465018</v>
+        <v>1.171113145591963</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>9.50714366218069</v>
+        <v>9.111012676256491</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09012804223657526</v>
+        <v>0.09027651273607823</v>
       </c>
       <c r="C26">
-        <v>1512040.975039225</v>
+        <v>1489503.476987856</v>
       </c>
       <c r="D26">
-        <v>1902238.835039224</v>
+        <v>1898587.926987856</v>
       </c>
       <c r="E26">
-        <v>372320.96</v>
+        <v>391207.55</v>
       </c>
       <c r="F26">
-        <v>453278.16</v>
+        <v>472164.75</v>
       </c>
       <c r="G26">
         <v>63080.3</v>
@@ -3425,45 +3425,45 @@
         <v>207730.1</v>
       </c>
       <c r="M26">
-        <v>22799.891448</v>
+        <v>24458.13405</v>
       </c>
       <c r="N26">
-        <v>184930.208552</v>
+        <v>183271.96595</v>
       </c>
       <c r="O26">
-        <v>36986.0417104</v>
+        <v>36654.39319</v>
       </c>
       <c r="P26">
-        <v>147944.1668416</v>
+        <v>146617.57276</v>
       </c>
       <c r="Q26">
-        <v>174941.6668416</v>
+        <v>173615.07276</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.105882160837599</v>
+        <v>0.106555350314771</v>
       </c>
       <c r="T26">
-        <v>1.171113145591963</v>
+        <v>1.18423486150896</v>
       </c>
       <c r="U26">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V26">
         <v>0.2</v>
       </c>
       <c r="W26">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y26">
-        <v>9.111012676256493</v>
+        <v>8.493293052337327</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09027651273607823</v>
+        <v>0.09013698323558124</v>
       </c>
       <c r="C27">
-        <v>1489503.476987856</v>
+        <v>1474047.537485289</v>
       </c>
       <c r="D27">
-        <v>1898587.926987856</v>
+        <v>1902018.577485289</v>
       </c>
       <c r="E27">
-        <v>391207.55</v>
+        <v>410094.14</v>
       </c>
       <c r="F27">
-        <v>472164.75</v>
+        <v>491051.34</v>
       </c>
       <c r="G27">
         <v>63080.3</v>
@@ -3507,28 +3507,28 @@
         <v>207730.1</v>
       </c>
       <c r="M27">
-        <v>24458.13405</v>
+        <v>25436.459412</v>
       </c>
       <c r="N27">
-        <v>183271.96595</v>
+        <v>182293.640588</v>
       </c>
       <c r="O27">
-        <v>36654.39319</v>
+        <v>36458.7281176</v>
       </c>
       <c r="P27">
-        <v>146617.57276</v>
+        <v>145834.9124704</v>
       </c>
       <c r="Q27">
-        <v>173615.07276</v>
+        <v>172832.4124704</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.106555350314771</v>
+        <v>0.1072467341021368</v>
       </c>
       <c r="T27">
-        <v>1.18423486150896</v>
+        <v>1.197711218396686</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.493293052337327</v>
+        <v>8.166627934939736</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09013698323558124</v>
+        <v>0.08999745373508423</v>
       </c>
       <c r="C28">
-        <v>1474047.537485289</v>
+        <v>1458604.018443</v>
       </c>
       <c r="D28">
-        <v>1902018.577485289</v>
+        <v>1905461.648442999</v>
       </c>
       <c r="E28">
-        <v>410094.14</v>
+        <v>428980.73</v>
       </c>
       <c r="F28">
-        <v>491051.34</v>
+        <v>509937.9300000001</v>
       </c>
       <c r="G28">
         <v>63080.3</v>
@@ -3589,28 +3589,28 @@
         <v>207730.1</v>
       </c>
       <c r="M28">
-        <v>25436.459412</v>
+        <v>26414.784774</v>
       </c>
       <c r="N28">
-        <v>182293.640588</v>
+        <v>181315.315226</v>
       </c>
       <c r="O28">
-        <v>36458.7281176</v>
+        <v>36263.0630452</v>
       </c>
       <c r="P28">
-        <v>145834.9124704</v>
+        <v>145052.2521808</v>
       </c>
       <c r="Q28">
-        <v>172832.4124704</v>
+        <v>172049.7521808</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1072467341021368</v>
+        <v>0.1079570599110743</v>
       </c>
       <c r="T28">
-        <v>1.197711218396686</v>
+        <v>1.211556790541611</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.166627934939736</v>
+        <v>7.864160233645672</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08999745373508423</v>
+        <v>0.08985792423458723</v>
       </c>
       <c r="C29">
-        <v>1458604.018443</v>
+        <v>1443172.987434585</v>
       </c>
       <c r="D29">
-        <v>1905461.648442999</v>
+        <v>1908917.207434585</v>
       </c>
       <c r="E29">
-        <v>428980.73</v>
+        <v>447867.32</v>
       </c>
       <c r="F29">
-        <v>509937.9300000001</v>
+        <v>528824.52</v>
       </c>
       <c r="G29">
         <v>63080.3</v>
@@ -3671,28 +3671,28 @@
         <v>207730.1</v>
       </c>
       <c r="M29">
-        <v>26414.784774</v>
+        <v>27393.110136</v>
       </c>
       <c r="N29">
-        <v>181315.315226</v>
+        <v>180336.989864</v>
       </c>
       <c r="O29">
-        <v>36263.0630452</v>
+        <v>36067.3979728</v>
       </c>
       <c r="P29">
-        <v>145052.2521808</v>
+        <v>144269.5918912</v>
       </c>
       <c r="Q29">
-        <v>172049.7521808</v>
+        <v>171267.0918912</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1079570599110743</v>
+        <v>0.1086871169924823</v>
       </c>
       <c r="T29">
-        <v>1.211556790541611</v>
+        <v>1.225786961912783</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>7.864160233645672</v>
+        <v>7.583297368158328</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08985792423458723</v>
+        <v>0.08971839473409021</v>
       </c>
       <c r="C30">
-        <v>1443172.987434585</v>
+        <v>1427754.512524714</v>
       </c>
       <c r="D30">
-        <v>1908917.207434585</v>
+        <v>1912385.322524714</v>
       </c>
       <c r="E30">
-        <v>447867.32</v>
+        <v>466753.9100000001</v>
       </c>
       <c r="F30">
-        <v>528824.52</v>
+        <v>547711.1100000001</v>
       </c>
       <c r="G30">
         <v>63080.3</v>
@@ -3753,28 +3753,28 @@
         <v>207730.1</v>
       </c>
       <c r="M30">
-        <v>27393.110136</v>
+        <v>28371.43549800001</v>
       </c>
       <c r="N30">
-        <v>180336.989864</v>
+        <v>179358.664502</v>
       </c>
       <c r="O30">
-        <v>36067.3979728</v>
+        <v>35871.7329004</v>
       </c>
       <c r="P30">
-        <v>144269.5918912</v>
+        <v>143486.9316016</v>
       </c>
       <c r="Q30">
-        <v>171267.0918912</v>
+        <v>170484.4316016</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1086871169924823</v>
+        <v>0.1094377390620989</v>
       </c>
       <c r="T30">
-        <v>1.225786961912783</v>
+        <v>1.240417983181735</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>7.583297368158328</v>
+        <v>7.321804355463211</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08971839473409021</v>
+        <v>0.08957886523359321</v>
       </c>
       <c r="C31">
-        <v>1427754.512524714</v>
+        <v>1412348.662273593</v>
       </c>
       <c r="D31">
-        <v>1912385.322524714</v>
+        <v>1915866.062273592</v>
       </c>
       <c r="E31">
-        <v>466753.91</v>
+        <v>485640.4999999999</v>
       </c>
       <c r="F31">
-        <v>547711.11</v>
+        <v>566597.7</v>
       </c>
       <c r="G31">
         <v>63080.3</v>
@@ -3835,28 +3835,28 @@
         <v>207730.1</v>
       </c>
       <c r="M31">
-        <v>28371.435498</v>
+        <v>29349.76086</v>
       </c>
       <c r="N31">
-        <v>179358.664502</v>
+        <v>178380.33914</v>
       </c>
       <c r="O31">
-        <v>35871.7329004</v>
+        <v>35676.067828</v>
       </c>
       <c r="P31">
-        <v>143486.9316016</v>
+        <v>142704.271312</v>
       </c>
       <c r="Q31">
-        <v>170484.4316016</v>
+        <v>169701.771312</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1094377390620989</v>
+        <v>0.1102098074765617</v>
       </c>
       <c r="T31">
-        <v>1.240417983181735</v>
+        <v>1.2554670336298</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>7.321804355463213</v>
+        <v>7.077744210281105</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08957886523359321</v>
+        <v>0.0894393357330962</v>
       </c>
       <c r="C32">
-        <v>1412348.662273593</v>
+        <v>1396955.505741485</v>
       </c>
       <c r="D32">
-        <v>1915866.062273592</v>
+        <v>1919359.495741485</v>
       </c>
       <c r="E32">
-        <v>485640.4999999999</v>
+        <v>504527.09</v>
       </c>
       <c r="F32">
-        <v>566597.7</v>
+        <v>585484.29</v>
       </c>
       <c r="G32">
         <v>63080.3</v>
@@ -3917,28 +3917,28 @@
         <v>207730.1</v>
       </c>
       <c r="M32">
-        <v>29349.76086</v>
+        <v>30328.086222</v>
       </c>
       <c r="N32">
-        <v>178380.33914</v>
+        <v>177402.013778</v>
       </c>
       <c r="O32">
-        <v>35676.067828</v>
+        <v>35480.4027556</v>
       </c>
       <c r="P32">
-        <v>142704.271312</v>
+        <v>141921.6110224</v>
       </c>
       <c r="Q32">
-        <v>169701.771312</v>
+        <v>168919.1110224</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1102098074765617</v>
+        <v>0.1110042546856467</v>
       </c>
       <c r="T32">
-        <v>1.2554670336298</v>
+        <v>1.270952288438678</v>
       </c>
       <c r="U32">
         <v>0.0518</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>7.077744210281105</v>
+        <v>6.849429880917199</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.0894393357330962</v>
+        <v>0.0897350062325992</v>
       </c>
       <c r="C33">
-        <v>1396955.505741485</v>
+        <v>1370681.190019405</v>
       </c>
       <c r="D33">
-        <v>1919359.495741485</v>
+        <v>1911971.770019405</v>
       </c>
       <c r="E33">
-        <v>504527.09</v>
+        <v>523413.68</v>
       </c>
       <c r="F33">
-        <v>585484.29</v>
+        <v>604370.88</v>
       </c>
       <c r="G33">
         <v>63080.3</v>
@@ -3999,45 +3999,45 @@
         <v>207730.1</v>
       </c>
       <c r="M33">
-        <v>30328.086222</v>
+        <v>32333.84208</v>
       </c>
       <c r="N33">
-        <v>177402.013778</v>
+        <v>175396.25792</v>
       </c>
       <c r="O33">
-        <v>35480.4027556</v>
+        <v>35079.25158400001</v>
       </c>
       <c r="P33">
-        <v>141921.6110224</v>
+        <v>140317.006336</v>
       </c>
       <c r="Q33">
-        <v>168919.1110224</v>
+        <v>167314.506336</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1110042546856467</v>
+        <v>0.1118220679891165</v>
       </c>
       <c r="T33">
-        <v>1.270952288438678</v>
+        <v>1.286892991918406</v>
       </c>
       <c r="U33">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V33">
         <v>0.2</v>
       </c>
       <c r="W33">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y33">
-        <v>6.849429880917199</v>
+        <v>6.424541181528527</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.0897350062325992</v>
+        <v>0.08960907673210218</v>
       </c>
       <c r="C34">
-        <v>1370681.190019405</v>
+        <v>1354934.15395019</v>
       </c>
       <c r="D34">
-        <v>1911971.770019405</v>
+        <v>1915111.32395019</v>
       </c>
       <c r="E34">
-        <v>523413.68</v>
+        <v>542300.27</v>
       </c>
       <c r="F34">
-        <v>604370.88</v>
+        <v>623257.47</v>
       </c>
       <c r="G34">
         <v>63080.3</v>
@@ -4081,28 +4081,28 @@
         <v>207730.1</v>
       </c>
       <c r="M34">
-        <v>32333.84208</v>
+        <v>33344.274645</v>
       </c>
       <c r="N34">
-        <v>175396.25792</v>
+        <v>174385.825355</v>
       </c>
       <c r="O34">
-        <v>35079.25158400001</v>
+        <v>34877.165071</v>
       </c>
       <c r="P34">
-        <v>140317.006336</v>
+        <v>139508.660284</v>
       </c>
       <c r="Q34">
-        <v>167314.506336</v>
+        <v>166506.160284</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1118220679891165</v>
+        <v>0.1126642936300033</v>
       </c>
       <c r="T34">
-        <v>1.286892991918406</v>
+        <v>1.30330953729305</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.424541181528527</v>
+        <v>6.229858115421602</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08960907673210218</v>
+        <v>0.08948314723160516</v>
       </c>
       <c r="C35">
-        <v>1354934.15395019</v>
+        <v>1339197.445450682</v>
       </c>
       <c r="D35">
-        <v>1915111.32395019</v>
+        <v>1918261.205450682</v>
       </c>
       <c r="E35">
-        <v>542300.27</v>
+        <v>561186.8600000001</v>
       </c>
       <c r="F35">
-        <v>623257.47</v>
+        <v>642144.0600000001</v>
       </c>
       <c r="G35">
         <v>63080.3</v>
@@ -4163,28 +4163,28 @@
         <v>207730.1</v>
       </c>
       <c r="M35">
-        <v>33344.274645</v>
+        <v>34354.70721</v>
       </c>
       <c r="N35">
-        <v>174385.825355</v>
+        <v>173375.39279</v>
       </c>
       <c r="O35">
-        <v>34877.165071</v>
+        <v>34675.078558</v>
       </c>
       <c r="P35">
-        <v>139508.660284</v>
+        <v>138700.314232</v>
       </c>
       <c r="Q35">
-        <v>166506.160284</v>
+        <v>165697.814232</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1126642936300033</v>
+        <v>0.1135320412600078</v>
       </c>
       <c r="T35">
-        <v>1.30330953729305</v>
+        <v>1.320223553739654</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.229858115421602</v>
+        <v>6.04662699437979</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08948314723160516</v>
+        <v>0.08935721773110818</v>
       </c>
       <c r="C36">
-        <v>1339197.445450682</v>
+        <v>1323471.115563677</v>
       </c>
       <c r="D36">
-        <v>1918261.205450682</v>
+        <v>1921421.465563677</v>
       </c>
       <c r="E36">
-        <v>561186.8600000001</v>
+        <v>580073.4500000001</v>
       </c>
       <c r="F36">
-        <v>642144.0600000001</v>
+        <v>661030.65</v>
       </c>
       <c r="G36">
         <v>63080.3</v>
@@ -4245,28 +4245,28 @@
         <v>207730.1</v>
       </c>
       <c r="M36">
-        <v>34354.70721</v>
+        <v>35365.139775</v>
       </c>
       <c r="N36">
-        <v>173375.39279</v>
+        <v>172364.960225</v>
       </c>
       <c r="O36">
-        <v>34675.078558</v>
+        <v>34472.992045</v>
       </c>
       <c r="P36">
-        <v>138700.314232</v>
+        <v>137891.96818</v>
       </c>
       <c r="Q36">
-        <v>165697.814232</v>
+        <v>164889.46818</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1135320412600078</v>
+        <v>0.1144264888170895</v>
       </c>
       <c r="T36">
-        <v>1.320223553739654</v>
+        <v>1.337658001461538</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>6.04662699437979</v>
+        <v>5.873866223111795</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08935721773110818</v>
+        <v>0.08923128823061116</v>
       </c>
       <c r="C37">
-        <v>1323471.115563677</v>
+        <v>1307755.215668895</v>
       </c>
       <c r="D37">
-        <v>1921421.465563677</v>
+        <v>1924592.155668895</v>
       </c>
       <c r="E37">
-        <v>580073.4500000001</v>
+        <v>598960.0400000002</v>
       </c>
       <c r="F37">
-        <v>661030.65</v>
+        <v>679917.2400000001</v>
       </c>
       <c r="G37">
         <v>63080.3</v>
@@ -4327,28 +4327,28 @@
         <v>207730.1</v>
       </c>
       <c r="M37">
-        <v>35365.139775</v>
+        <v>36375.57234000001</v>
       </c>
       <c r="N37">
-        <v>172364.960225</v>
+        <v>171354.52766</v>
       </c>
       <c r="O37">
-        <v>34472.992045</v>
+        <v>34270.905532</v>
       </c>
       <c r="P37">
-        <v>137891.96818</v>
+        <v>137083.622128</v>
       </c>
       <c r="Q37">
-        <v>164889.46818</v>
+        <v>164081.122128</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1144264888170895</v>
+        <v>0.11534888786033</v>
       </c>
       <c r="T37">
-        <v>1.337658001461538</v>
+        <v>1.355637275674731</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.873866223111795</v>
+        <v>5.710703272469801</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08923128823061117</v>
+        <v>0.08934215873011417</v>
       </c>
       <c r="C38">
-        <v>1307755.215668894</v>
+        <v>1286076.545470197</v>
       </c>
       <c r="D38">
-        <v>1924592.155668894</v>
+        <v>1921800.075470197</v>
       </c>
       <c r="E38">
-        <v>598960.04</v>
+        <v>617846.63</v>
       </c>
       <c r="F38">
-        <v>679917.24</v>
+        <v>698803.83</v>
       </c>
       <c r="G38">
         <v>63080.3</v>
@@ -4409,45 +4409,45 @@
         <v>207730.1</v>
       </c>
       <c r="M38">
-        <v>36375.57234</v>
+        <v>37945.047969</v>
       </c>
       <c r="N38">
-        <v>171354.52766</v>
+        <v>169785.052031</v>
       </c>
       <c r="O38">
-        <v>34270.905532</v>
+        <v>33957.0104062</v>
       </c>
       <c r="P38">
-        <v>137083.622128</v>
+        <v>135828.0416248</v>
       </c>
       <c r="Q38">
-        <v>164081.122128</v>
+        <v>162825.5416248</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.11534888786033</v>
+        <v>0.1163005694128796</v>
       </c>
       <c r="T38">
-        <v>1.355637275674731</v>
+        <v>1.374187320497866</v>
       </c>
       <c r="U38">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V38">
         <v>0.2</v>
       </c>
       <c r="W38">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y38">
-        <v>5.710703272469803</v>
+        <v>5.47449828419533</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08934215873011417</v>
+        <v>0.08922262922961716</v>
       </c>
       <c r="C39">
-        <v>1286076.545470197</v>
+        <v>1270200.439101766</v>
       </c>
       <c r="D39">
-        <v>1921800.075470197</v>
+        <v>1924810.559101766</v>
       </c>
       <c r="E39">
-        <v>617846.63</v>
+        <v>636733.2200000001</v>
       </c>
       <c r="F39">
-        <v>698803.83</v>
+        <v>717690.42</v>
       </c>
       <c r="G39">
         <v>63080.3</v>
@@ -4491,28 +4491,28 @@
         <v>207730.1</v>
       </c>
       <c r="M39">
-        <v>37945.047969</v>
+        <v>38970.589806</v>
       </c>
       <c r="N39">
-        <v>169785.052031</v>
+        <v>168759.510194</v>
       </c>
       <c r="O39">
-        <v>33957.0104062</v>
+        <v>33751.9020388</v>
       </c>
       <c r="P39">
-        <v>135828.0416248</v>
+        <v>135007.6081552</v>
       </c>
       <c r="Q39">
-        <v>162825.5416248</v>
+        <v>162005.1081552</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1163005694128796</v>
+        <v>0.1172829503703502</v>
       </c>
       <c r="T39">
-        <v>1.374187320497866</v>
+        <v>1.393335753863683</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.47449828419533</v>
+        <v>5.3304325398744</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08922262922961716</v>
+        <v>0.08910309972912014</v>
       </c>
       <c r="C40">
-        <v>1270200.439101766</v>
+        <v>1254333.779325848</v>
       </c>
       <c r="D40">
-        <v>1924810.559101766</v>
+        <v>1927830.489325848</v>
       </c>
       <c r="E40">
-        <v>636733.2200000001</v>
+        <v>655619.8100000001</v>
       </c>
       <c r="F40">
-        <v>717690.42</v>
+        <v>736577.01</v>
       </c>
       <c r="G40">
         <v>63080.3</v>
@@ -4573,28 +4573,28 @@
         <v>207730.1</v>
       </c>
       <c r="M40">
-        <v>38970.589806</v>
+        <v>39996.131643</v>
       </c>
       <c r="N40">
-        <v>168759.510194</v>
+        <v>167733.968357</v>
       </c>
       <c r="O40">
-        <v>33751.9020388</v>
+        <v>33546.7936714</v>
       </c>
       <c r="P40">
-        <v>135007.6081552</v>
+        <v>134187.1746856</v>
       </c>
       <c r="Q40">
-        <v>162005.1081552</v>
+        <v>161184.6746856</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1172829503703502</v>
+        <v>0.1182975405395412</v>
       </c>
       <c r="T40">
-        <v>1.393335753863683</v>
+        <v>1.413112004716904</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.3304325398744</v>
+        <v>5.193754782441723</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08910309972912014</v>
+        <v>0.08898357022862315</v>
       </c>
       <c r="C41">
-        <v>1254333.779325848</v>
+        <v>1238476.610675988</v>
       </c>
       <c r="D41">
-        <v>1927830.489325848</v>
+        <v>1930859.910675988</v>
       </c>
       <c r="E41">
-        <v>655619.8100000001</v>
+        <v>674506.4000000001</v>
       </c>
       <c r="F41">
-        <v>736577.01</v>
+        <v>755463.6000000001</v>
       </c>
       <c r="G41">
         <v>63080.3</v>
@@ -4655,28 +4655,28 @@
         <v>207730.1</v>
       </c>
       <c r="M41">
-        <v>39996.131643</v>
+        <v>41021.67348</v>
       </c>
       <c r="N41">
-        <v>167733.968357</v>
+        <v>166708.42652</v>
       </c>
       <c r="O41">
-        <v>33546.7936714</v>
+        <v>33341.68530400001</v>
       </c>
       <c r="P41">
-        <v>134187.1746856</v>
+        <v>133366.741216</v>
       </c>
       <c r="Q41">
-        <v>161184.6746856</v>
+        <v>160364.241216</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1182975405395412</v>
+        <v>0.1193459503810386</v>
       </c>
       <c r="T41">
-        <v>1.413112004716904</v>
+        <v>1.433547463931899</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.193754782441723</v>
+        <v>5.06391091288068</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08898357022862315</v>
+        <v>0.08886404072812613</v>
       </c>
       <c r="C42">
-        <v>1238476.610675988</v>
+        <v>1222628.977966096</v>
       </c>
       <c r="D42">
-        <v>1930859.910675988</v>
+        <v>1933898.867966096</v>
       </c>
       <c r="E42">
-        <v>674506.4000000001</v>
+        <v>693392.9900000001</v>
       </c>
       <c r="F42">
-        <v>755463.6000000001</v>
+        <v>774350.1900000001</v>
       </c>
       <c r="G42">
         <v>63080.3</v>
@@ -4737,28 +4737,28 @@
         <v>207730.1</v>
       </c>
       <c r="M42">
-        <v>41021.67348</v>
+        <v>42047.215317</v>
       </c>
       <c r="N42">
-        <v>166708.42652</v>
+        <v>165682.884683</v>
       </c>
       <c r="O42">
-        <v>33341.68530400001</v>
+        <v>33136.5769366</v>
       </c>
       <c r="P42">
-        <v>133366.741216</v>
+        <v>132546.3077464</v>
       </c>
       <c r="Q42">
-        <v>160364.241216</v>
+        <v>159543.8077464</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1193459503810386</v>
+        <v>0.1204298995391968</v>
       </c>
       <c r="T42">
-        <v>1.433547463931899</v>
+        <v>1.454675650577911</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.06391091288068</v>
+        <v>4.940400890615298</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08886404072812613</v>
+        <v>0.08874451122762914</v>
       </c>
       <c r="C43">
-        <v>1222628.977966096</v>
+        <v>1206790.926292652</v>
       </c>
       <c r="D43">
-        <v>1933898.867966096</v>
+        <v>1936947.406292652</v>
       </c>
       <c r="E43">
-        <v>693392.9900000001</v>
+        <v>712279.5800000001</v>
       </c>
       <c r="F43">
-        <v>774350.1900000001</v>
+        <v>793236.78</v>
       </c>
       <c r="G43">
         <v>63080.3</v>
@@ -4819,28 +4819,28 @@
         <v>207730.1</v>
       </c>
       <c r="M43">
-        <v>42047.215317</v>
+        <v>43072.757154</v>
       </c>
       <c r="N43">
-        <v>165682.884683</v>
+        <v>164657.342846</v>
       </c>
       <c r="O43">
-        <v>33136.5769366</v>
+        <v>32931.46856920001</v>
       </c>
       <c r="P43">
-        <v>132546.3077464</v>
+        <v>131725.8742768</v>
       </c>
       <c r="Q43">
-        <v>159543.8077464</v>
+        <v>158723.3742768</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1204298995391968</v>
+        <v>0.121551226254533</v>
       </c>
       <c r="T43">
-        <v>1.454675650577911</v>
+        <v>1.47653239538413</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.940400890615298</v>
+        <v>4.822772297981601</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08874451122762915</v>
+        <v>0.08862498172713215</v>
       </c>
       <c r="C44">
-        <v>1206790.926292652</v>
+        <v>1190962.501036944</v>
       </c>
       <c r="D44">
-        <v>1936947.406292652</v>
+        <v>1940005.571036944</v>
       </c>
       <c r="E44">
-        <v>712279.5800000001</v>
+        <v>731166.17</v>
       </c>
       <c r="F44">
-        <v>793236.78</v>
+        <v>812123.37</v>
       </c>
       <c r="G44">
         <v>63080.3</v>
@@ -4901,28 +4901,28 @@
         <v>207730.1</v>
       </c>
       <c r="M44">
-        <v>43072.757154</v>
+        <v>44098.298991</v>
       </c>
       <c r="N44">
-        <v>164657.342846</v>
+        <v>163631.801009</v>
       </c>
       <c r="O44">
-        <v>32931.46856920001</v>
+        <v>32726.3602018</v>
       </c>
       <c r="P44">
-        <v>131725.8742768</v>
+        <v>130905.4408072</v>
       </c>
       <c r="Q44">
-        <v>158723.3742768</v>
+        <v>157902.9408072</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.121551226254533</v>
+        <v>0.1227118977668985</v>
       </c>
       <c r="T44">
-        <v>1.47653239538413</v>
+        <v>1.499156043516883</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.822772297981601</v>
+        <v>4.710614802679702</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08862498172713215</v>
+        <v>0.08850545222663511</v>
       </c>
       <c r="C45">
-        <v>1190962.501036944</v>
+        <v>1175143.747867313</v>
       </c>
       <c r="D45">
-        <v>1940005.571036944</v>
+        <v>1943073.407867313</v>
       </c>
       <c r="E45">
-        <v>731166.17</v>
+        <v>750052.76</v>
       </c>
       <c r="F45">
-        <v>812123.37</v>
+        <v>831009.96</v>
       </c>
       <c r="G45">
         <v>63080.3</v>
@@ -4983,28 +4983,28 @@
         <v>207730.1</v>
       </c>
       <c r="M45">
-        <v>44098.298991</v>
+        <v>45123.840828</v>
       </c>
       <c r="N45">
-        <v>163631.801009</v>
+        <v>162606.259172</v>
       </c>
       <c r="O45">
-        <v>32726.3602018</v>
+        <v>32521.2518344</v>
       </c>
       <c r="P45">
-        <v>130905.4408072</v>
+        <v>130085.0073376</v>
       </c>
       <c r="Q45">
-        <v>157902.9408072</v>
+        <v>157082.5073376</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1227118977668985</v>
+        <v>0.123914021833277</v>
       </c>
       <c r="T45">
-        <v>1.499156043516883</v>
+        <v>1.522587679082949</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.710614802679702</v>
+        <v>4.603555375346073</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08850545222663511</v>
+        <v>0.08838592272613813</v>
       </c>
       <c r="C46">
-        <v>1175143.747867313</v>
+        <v>1159334.712741427</v>
       </c>
       <c r="D46">
-        <v>1943073.407867313</v>
+        <v>1946150.962741427</v>
       </c>
       <c r="E46">
-        <v>750052.76</v>
+        <v>768939.3500000001</v>
       </c>
       <c r="F46">
-        <v>831009.96</v>
+        <v>849896.55</v>
       </c>
       <c r="G46">
         <v>63080.3</v>
@@ -5065,28 +5065,28 @@
         <v>207730.1</v>
       </c>
       <c r="M46">
-        <v>45123.840828</v>
+        <v>46149.382665</v>
       </c>
       <c r="N46">
-        <v>162606.259172</v>
+        <v>161580.717335</v>
       </c>
       <c r="O46">
-        <v>32521.2518344</v>
+        <v>32316.143467</v>
       </c>
       <c r="P46">
-        <v>130085.0073376</v>
+        <v>129264.573868</v>
       </c>
       <c r="Q46">
-        <v>157082.5073376</v>
+        <v>156262.073868</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.123914021833277</v>
+        <v>0.1251598595020693</v>
       </c>
       <c r="T46">
-        <v>1.522587679082949</v>
+        <v>1.546871374124144</v>
       </c>
       <c r="U46">
         <v>0.0543</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.603555375346073</v>
+        <v>4.501254144782827</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08838592272613813</v>
+        <v>0.08826639322564112</v>
       </c>
       <c r="C47">
-        <v>1159334.712741427</v>
+        <v>1143535.441908583</v>
       </c>
       <c r="D47">
-        <v>1946150.962741427</v>
+        <v>1949238.281908583</v>
       </c>
       <c r="E47">
-        <v>768939.3500000001</v>
+        <v>787825.9400000001</v>
       </c>
       <c r="F47">
-        <v>849896.55</v>
+        <v>868783.14</v>
       </c>
       <c r="G47">
         <v>63080.3</v>
@@ -5147,28 +5147,28 @@
         <v>207730.1</v>
       </c>
       <c r="M47">
-        <v>46149.382665</v>
+        <v>47174.924502</v>
       </c>
       <c r="N47">
-        <v>161580.717335</v>
+        <v>160555.175498</v>
       </c>
       <c r="O47">
-        <v>32316.143467</v>
+        <v>32111.0350996</v>
       </c>
       <c r="P47">
-        <v>129264.573868</v>
+        <v>128444.1403984</v>
       </c>
       <c r="Q47">
-        <v>156262.073868</v>
+        <v>155441.6403984</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1251598595020693</v>
+        <v>0.1264518393067428</v>
       </c>
       <c r="T47">
-        <v>1.546871374124144</v>
+        <v>1.572054465277976</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.501254144782827</v>
+        <v>4.403400793809287</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08826639322564112</v>
+        <v>0.0881468637251441</v>
       </c>
       <c r="C48">
-        <v>1143535.441908583</v>
+        <v>1127745.981912014</v>
       </c>
       <c r="D48">
-        <v>1949238.281908583</v>
+        <v>1952335.411912014</v>
       </c>
       <c r="E48">
-        <v>787825.9400000001</v>
+        <v>806712.5300000001</v>
       </c>
       <c r="F48">
-        <v>868783.14</v>
+        <v>887669.7300000001</v>
       </c>
       <c r="G48">
         <v>63080.3</v>
@@ -5229,28 +5229,28 @@
         <v>207730.1</v>
       </c>
       <c r="M48">
-        <v>47174.924502</v>
+        <v>48200.46633900001</v>
       </c>
       <c r="N48">
-        <v>160555.175498</v>
+        <v>159529.633661</v>
       </c>
       <c r="O48">
-        <v>32111.0350996</v>
+        <v>31905.9267322</v>
       </c>
       <c r="P48">
-        <v>128444.1403984</v>
+        <v>127623.7069288</v>
       </c>
       <c r="Q48">
-        <v>155441.6403984</v>
+        <v>154621.2069288</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1264518393067428</v>
+        <v>0.1277925730663096</v>
       </c>
       <c r="T48">
-        <v>1.572054465277976</v>
+        <v>1.598187861758368</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.403400793809287</v>
+        <v>4.3097114152176</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.0881468637251441</v>
+        <v>0.08841133422464709</v>
       </c>
       <c r="C49">
-        <v>1127745.981912014</v>
+        <v>1102019.851064103</v>
       </c>
       <c r="D49">
-        <v>1952335.411912014</v>
+        <v>1945495.871064103</v>
       </c>
       <c r="E49">
-        <v>806712.5300000001</v>
+        <v>825599.1200000001</v>
       </c>
       <c r="F49">
-        <v>887669.7300000001</v>
+        <v>906556.3200000001</v>
       </c>
       <c r="G49">
         <v>63080.3</v>
@@ -5311,45 +5311,45 @@
         <v>207730.1</v>
       </c>
       <c r="M49">
-        <v>48200.46633900001</v>
+        <v>50132.56449600001</v>
       </c>
       <c r="N49">
-        <v>159529.633661</v>
+        <v>157597.535504</v>
       </c>
       <c r="O49">
-        <v>31905.9267322</v>
+        <v>31519.5071008</v>
       </c>
       <c r="P49">
-        <v>127623.7069288</v>
+        <v>126078.0284032</v>
       </c>
       <c r="Q49">
-        <v>154621.2069288</v>
+        <v>153075.5284032</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1277925730663096</v>
+        <v>0.1291848735089367</v>
       </c>
       <c r="T49">
-        <v>1.598187861758368</v>
+        <v>1.625326388872621</v>
       </c>
       <c r="U49">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V49">
         <v>0.2</v>
       </c>
       <c r="W49">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y49">
-        <v>4.3097114152176</v>
+        <v>4.143616072474698</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08841133422464709</v>
+        <v>0.08829980472415008</v>
       </c>
       <c r="C50">
-        <v>1102019.851064103</v>
+        <v>1086011.702732123</v>
       </c>
       <c r="D50">
-        <v>1945495.871064103</v>
+        <v>1948374.312732123</v>
       </c>
       <c r="E50">
-        <v>825599.12</v>
+        <v>844485.7100000001</v>
       </c>
       <c r="F50">
-        <v>906556.3199999999</v>
+        <v>925442.91</v>
       </c>
       <c r="G50">
         <v>63080.3</v>
@@ -5393,28 +5393,28 @@
         <v>207730.1</v>
       </c>
       <c r="M50">
-        <v>50132.564496</v>
+        <v>51176.99292300001</v>
       </c>
       <c r="N50">
-        <v>157597.535504</v>
+        <v>156553.107077</v>
       </c>
       <c r="O50">
-        <v>31519.5071008</v>
+        <v>31310.6214154</v>
       </c>
       <c r="P50">
-        <v>126078.0284032</v>
+        <v>125242.4856616</v>
       </c>
       <c r="Q50">
-        <v>153075.5284032</v>
+        <v>152239.9856616</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1291848735089367</v>
+        <v>0.1306317739689217</v>
       </c>
       <c r="T50">
-        <v>1.625326388872621</v>
+        <v>1.653529171952139</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.143616072474698</v>
+        <v>4.059052479158887</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08829980472415008</v>
+        <v>0.08818827522365308</v>
       </c>
       <c r="C51">
-        <v>1086011.702732123</v>
+        <v>1070012.08456806</v>
       </c>
       <c r="D51">
-        <v>1948374.312732123</v>
+        <v>1951261.28456806</v>
       </c>
       <c r="E51">
-        <v>844485.7100000001</v>
+        <v>863372.3</v>
       </c>
       <c r="F51">
-        <v>925442.91</v>
+        <v>944329.5</v>
       </c>
       <c r="G51">
         <v>63080.3</v>
@@ -5475,28 +5475,28 @@
         <v>207730.1</v>
       </c>
       <c r="M51">
-        <v>51176.99292300001</v>
+        <v>52221.42135</v>
       </c>
       <c r="N51">
-        <v>156553.107077</v>
+        <v>155508.67865</v>
       </c>
       <c r="O51">
-        <v>31310.6214154</v>
+        <v>31101.73573</v>
       </c>
       <c r="P51">
-        <v>125242.4856616</v>
+        <v>124406.94292</v>
       </c>
       <c r="Q51">
-        <v>152239.9856616</v>
+        <v>151404.44292</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1306317739689217</v>
+        <v>0.1321365504473062</v>
       </c>
       <c r="T51">
-        <v>1.653529171952139</v>
+        <v>1.682860066354838</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.059052479158887</v>
+        <v>3.97787142957571</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08818827522365308</v>
+        <v>0.08807674572315606</v>
       </c>
       <c r="C52">
-        <v>1070012.08456806</v>
+        <v>1054021.034546494</v>
       </c>
       <c r="D52">
-        <v>1951261.28456806</v>
+        <v>1954156.824546494</v>
       </c>
       <c r="E52">
-        <v>863372.3</v>
+        <v>882258.89</v>
       </c>
       <c r="F52">
-        <v>944329.5</v>
+        <v>963216.09</v>
       </c>
       <c r="G52">
         <v>63080.3</v>
@@ -5557,28 +5557,28 @@
         <v>207730.1</v>
       </c>
       <c r="M52">
-        <v>52221.42135</v>
+        <v>53265.849777</v>
       </c>
       <c r="N52">
-        <v>155508.67865</v>
+        <v>154464.250223</v>
       </c>
       <c r="O52">
-        <v>31101.73573</v>
+        <v>30892.8500446</v>
       </c>
       <c r="P52">
-        <v>124406.94292</v>
+        <v>123571.4001784</v>
       </c>
       <c r="Q52">
-        <v>151404.44292</v>
+        <v>150568.9001784</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1321365504473062</v>
+        <v>0.1337027463737879</v>
       </c>
       <c r="T52">
-        <v>1.682860066354838</v>
+        <v>1.713388140120912</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.97787142957571</v>
+        <v>3.899873950564421</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08807674572315606</v>
+        <v>0.08796521622265906</v>
       </c>
       <c r="C53">
-        <v>1054021.034546494</v>
+        <v>1038038.590867747</v>
       </c>
       <c r="D53">
-        <v>1954156.824546494</v>
+        <v>1957060.970867747</v>
       </c>
       <c r="E53">
-        <v>882258.89</v>
+        <v>901145.4800000001</v>
       </c>
       <c r="F53">
-        <v>963216.09</v>
+        <v>982102.6800000001</v>
       </c>
       <c r="G53">
         <v>63080.3</v>
@@ -5639,28 +5639,28 @@
         <v>207730.1</v>
       </c>
       <c r="M53">
-        <v>53265.849777</v>
+        <v>54310.278204</v>
       </c>
       <c r="N53">
-        <v>154464.250223</v>
+        <v>153419.821796</v>
       </c>
       <c r="O53">
-        <v>30892.8500446</v>
+        <v>30683.9643592</v>
       </c>
       <c r="P53">
-        <v>123571.4001784</v>
+        <v>122735.8574368</v>
       </c>
       <c r="Q53">
-        <v>150568.9001784</v>
+        <v>149733.3574368</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1337027463737879</v>
+        <v>0.135334200463873</v>
       </c>
       <c r="T53">
-        <v>1.713388140120912</v>
+        <v>1.745188216960573</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.899873950564421</v>
+        <v>3.824876374592029</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08796521622265906</v>
+        <v>0.08785368672216207</v>
       </c>
       <c r="C54">
-        <v>1038038.590867747</v>
+        <v>1022064.79195956</v>
       </c>
       <c r="D54">
-        <v>1957060.970867747</v>
+        <v>1959973.76195956</v>
       </c>
       <c r="E54">
-        <v>901145.4800000001</v>
+        <v>920032.0700000001</v>
       </c>
       <c r="F54">
-        <v>982102.6800000001</v>
+        <v>1000989.27</v>
       </c>
       <c r="G54">
         <v>63080.3</v>
@@ -5721,28 +5721,28 @@
         <v>207730.1</v>
       </c>
       <c r="M54">
-        <v>54310.278204</v>
+        <v>55354.706631</v>
       </c>
       <c r="N54">
-        <v>153419.821796</v>
+        <v>152375.393369</v>
       </c>
       <c r="O54">
-        <v>30683.9643592</v>
+        <v>30475.0786738</v>
       </c>
       <c r="P54">
-        <v>122735.8574368</v>
+        <v>121900.3146952</v>
       </c>
       <c r="Q54">
-        <v>149733.3574368</v>
+        <v>148897.8146952</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.135334200463873</v>
+        <v>0.1370350781322597</v>
       </c>
       <c r="T54">
-        <v>1.745188216960573</v>
+        <v>1.778341488559368</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.824876374592029</v>
+        <v>3.752708895826141</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08785368672216207</v>
+        <v>0.08774215722166503</v>
       </c>
       <c r="C55">
-        <v>1022064.79195956</v>
+        <v>1006099.676478795</v>
       </c>
       <c r="D55">
-        <v>1959973.76195956</v>
+        <v>1962895.236478796</v>
       </c>
       <c r="E55">
-        <v>920032.0700000001</v>
+        <v>938918.6600000001</v>
       </c>
       <c r="F55">
-        <v>1000989.27</v>
+        <v>1019875.86</v>
       </c>
       <c r="G55">
         <v>63080.3</v>
@@ -5803,28 +5803,28 @@
         <v>207730.1</v>
       </c>
       <c r="M55">
-        <v>55354.706631</v>
+        <v>56399.13505800001</v>
       </c>
       <c r="N55">
-        <v>152375.393369</v>
+        <v>151330.964942</v>
       </c>
       <c r="O55">
-        <v>30475.0786738</v>
+        <v>30266.1929884</v>
       </c>
       <c r="P55">
-        <v>121900.3146952</v>
+        <v>121064.7719536</v>
       </c>
       <c r="Q55">
-        <v>148897.8146952</v>
+        <v>148062.2719536</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1370350781322597</v>
+        <v>0.1388099070036197</v>
       </c>
       <c r="T55">
-        <v>1.778341488559368</v>
+        <v>1.812936206749415</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.752708895826141</v>
+        <v>3.683214286644175</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08774215722166503</v>
+        <v>0.08763062772116804</v>
       </c>
       <c r="C56">
-        <v>1006099.676478795</v>
+        <v>990143.2833131378</v>
       </c>
       <c r="D56">
-        <v>1962895.236478796</v>
+        <v>1965825.433313138</v>
       </c>
       <c r="E56">
-        <v>938918.6600000001</v>
+        <v>957805.2500000001</v>
       </c>
       <c r="F56">
-        <v>1019875.86</v>
+        <v>1038762.45</v>
       </c>
       <c r="G56">
         <v>63080.3</v>
@@ -5885,28 +5885,28 @@
         <v>207730.1</v>
       </c>
       <c r="M56">
-        <v>56399.13505800001</v>
+        <v>57443.56348500001</v>
       </c>
       <c r="N56">
-        <v>151330.964942</v>
+        <v>150286.536515</v>
       </c>
       <c r="O56">
-        <v>30266.1929884</v>
+        <v>30057.307303</v>
       </c>
       <c r="P56">
-        <v>121064.7719536</v>
+        <v>120229.229212</v>
       </c>
       <c r="Q56">
-        <v>148062.2719536</v>
+        <v>147226.729212</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1388099070036197</v>
+        <v>0.1406636171581512</v>
       </c>
       <c r="T56">
-        <v>1.812936206749415</v>
+        <v>1.849068467970131</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.683214286644175</v>
+        <v>3.616246754159736</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08763062772116804</v>
+        <v>0.08751909822067103</v>
       </c>
       <c r="C57">
-        <v>990143.2833131378</v>
+        <v>974195.6515828269</v>
       </c>
       <c r="D57">
-        <v>1965825.433313138</v>
+        <v>1968764.391582827</v>
       </c>
       <c r="E57">
-        <v>957805.2500000001</v>
+        <v>976691.8400000001</v>
       </c>
       <c r="F57">
-        <v>1038762.45</v>
+        <v>1057649.04</v>
       </c>
       <c r="G57">
         <v>63080.3</v>
@@ -5967,28 +5967,28 @@
         <v>207730.1</v>
       </c>
       <c r="M57">
-        <v>57443.56348500001</v>
+        <v>58487.991912</v>
       </c>
       <c r="N57">
-        <v>150286.536515</v>
+        <v>149242.108088</v>
       </c>
       <c r="O57">
-        <v>30057.307303</v>
+        <v>29848.4216176</v>
       </c>
       <c r="P57">
-        <v>120229.229212</v>
+        <v>119393.6864704</v>
       </c>
       <c r="Q57">
-        <v>147226.729212</v>
+        <v>146391.1864704</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1406636171581512</v>
+        <v>0.1426015868651614</v>
       </c>
       <c r="T57">
-        <v>1.849068467970131</v>
+        <v>1.886843104700879</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.616246754159736</v>
+        <v>3.551670919264027</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08751909822067103</v>
+        <v>0.08740756872017402</v>
       </c>
       <c r="C58">
-        <v>974195.6515828269</v>
+        <v>958256.8206423938</v>
       </c>
       <c r="D58">
-        <v>1968764.391582827</v>
+        <v>1971712.150642394</v>
       </c>
       <c r="E58">
-        <v>976691.8400000001</v>
+        <v>995578.4300000002</v>
       </c>
       <c r="F58">
-        <v>1057649.04</v>
+        <v>1076535.63</v>
       </c>
       <c r="G58">
         <v>63080.3</v>
@@ -6049,28 +6049,28 @@
         <v>207730.1</v>
       </c>
       <c r="M58">
-        <v>58487.991912</v>
+        <v>59532.42033900001</v>
       </c>
       <c r="N58">
-        <v>149242.108088</v>
+        <v>148197.679661</v>
       </c>
       <c r="O58">
-        <v>29848.4216176</v>
+        <v>29639.5359322</v>
       </c>
       <c r="P58">
-        <v>119393.6864704</v>
+        <v>118558.1437288</v>
       </c>
       <c r="Q58">
-        <v>146391.1864704</v>
+        <v>145555.6437288</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1426015868651614</v>
+        <v>0.1446296946980792</v>
       </c>
       <c r="T58">
-        <v>1.886843104700879</v>
+        <v>1.926374701279569</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.551670919264027</v>
+        <v>3.489360903136587</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08740756872017402</v>
+        <v>0.08729603921967702</v>
       </c>
       <c r="C59">
-        <v>958256.8206423938</v>
+        <v>942326.830082421</v>
       </c>
       <c r="D59">
-        <v>1971712.150642394</v>
+        <v>1974668.750082421</v>
       </c>
       <c r="E59">
-        <v>995578.4300000002</v>
+        <v>1014465.02</v>
       </c>
       <c r="F59">
-        <v>1076535.63</v>
+        <v>1095422.22</v>
       </c>
       <c r="G59">
         <v>63080.3</v>
@@ -6131,28 +6131,28 @@
         <v>207730.1</v>
       </c>
       <c r="M59">
-        <v>59532.42033900001</v>
+        <v>60576.84876600001</v>
       </c>
       <c r="N59">
-        <v>148197.679661</v>
+        <v>147153.251234</v>
       </c>
       <c r="O59">
-        <v>29639.5359322</v>
+        <v>29430.6502468</v>
       </c>
       <c r="P59">
-        <v>118558.1437288</v>
+        <v>117722.6009872</v>
       </c>
       <c r="Q59">
-        <v>145555.6437288</v>
+        <v>144720.1009872</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1446296946980792</v>
+        <v>0.1467543790944691</v>
       </c>
       <c r="T59">
-        <v>1.926374701279569</v>
+        <v>1.967788754838197</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.489360903136587</v>
+        <v>3.429199508254922</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08729603921967702</v>
+        <v>0.08718450971918001</v>
       </c>
       <c r="C60">
-        <v>942326.8300824212</v>
+        <v>926405.7197313127</v>
       </c>
       <c r="D60">
-        <v>1974668.750082421</v>
+        <v>1977634.229731313</v>
       </c>
       <c r="E60">
-        <v>1014465.02</v>
+        <v>1033351.61</v>
       </c>
       <c r="F60">
-        <v>1095422.22</v>
+        <v>1114308.81</v>
       </c>
       <c r="G60">
         <v>63080.3</v>
@@ -6213,28 +6213,28 @@
         <v>207730.1</v>
       </c>
       <c r="M60">
-        <v>60576.848766</v>
+        <v>61621.277193</v>
       </c>
       <c r="N60">
-        <v>147153.251234</v>
+        <v>146108.822807</v>
       </c>
       <c r="O60">
-        <v>29430.6502468</v>
+        <v>29221.76456140001</v>
       </c>
       <c r="P60">
-        <v>117722.6009872</v>
+        <v>116887.0582456</v>
       </c>
       <c r="Q60">
-        <v>144720.1009872</v>
+        <v>143884.5582456</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1467543790944691</v>
+        <v>0.1489827066321464</v>
       </c>
       <c r="T60">
-        <v>1.967788754838196</v>
+        <v>2.011223006131392</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.429199508254922</v>
+        <v>3.37107748269128</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08718450971918001</v>
+        <v>0.08707298021868301</v>
       </c>
       <c r="C61">
-        <v>926405.7197313127</v>
+        <v>910493.529657084</v>
       </c>
       <c r="D61">
-        <v>1977634.229731313</v>
+        <v>1980608.629657084</v>
       </c>
       <c r="E61">
-        <v>1033351.61</v>
+        <v>1052238.2</v>
       </c>
       <c r="F61">
-        <v>1114308.81</v>
+        <v>1133195.4</v>
       </c>
       <c r="G61">
         <v>63080.3</v>
@@ -6295,28 +6295,28 @@
         <v>207730.1</v>
       </c>
       <c r="M61">
-        <v>61621.277193</v>
+        <v>62665.70562</v>
       </c>
       <c r="N61">
-        <v>146108.822807</v>
+        <v>145064.39438</v>
       </c>
       <c r="O61">
-        <v>29221.76456140001</v>
+        <v>29012.878876</v>
       </c>
       <c r="P61">
-        <v>116887.0582456</v>
+        <v>116051.515504</v>
       </c>
       <c r="Q61">
-        <v>143884.5582456</v>
+        <v>143049.015504</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1489827066321464</v>
+        <v>0.1513224505467075</v>
       </c>
       <c r="T61">
-        <v>2.011223006131392</v>
+        <v>2.056828969989247</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.37107748269128</v>
+        <v>3.314892857979758</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08707298021868301</v>
+        <v>0.08696145071818601</v>
       </c>
       <c r="C62">
-        <v>910493.529657084</v>
+        <v>894590.3001691641</v>
       </c>
       <c r="D62">
-        <v>1980608.629657084</v>
+        <v>1983591.990169164</v>
       </c>
       <c r="E62">
-        <v>1052238.2</v>
+        <v>1071124.79</v>
       </c>
       <c r="F62">
-        <v>1133195.4</v>
+        <v>1152081.99</v>
       </c>
       <c r="G62">
         <v>63080.3</v>
@@ -6377,28 +6377,28 @@
         <v>207730.1</v>
       </c>
       <c r="M62">
-        <v>62665.70562</v>
+        <v>63710.134047</v>
       </c>
       <c r="N62">
-        <v>145064.39438</v>
+        <v>144019.965953</v>
       </c>
       <c r="O62">
-        <v>29012.878876</v>
+        <v>28803.9931906</v>
       </c>
       <c r="P62">
-        <v>116051.515504</v>
+        <v>115215.9727624</v>
       </c>
       <c r="Q62">
-        <v>143049.015504</v>
+        <v>142213.4727624</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1513224505467075</v>
+        <v>0.153782181328682</v>
       </c>
       <c r="T62">
-        <v>2.056828969989247</v>
+        <v>2.104773701224427</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.314892857979758</v>
+        <v>3.260550352111238</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08696145071818601</v>
+        <v>0.086849921217689</v>
       </c>
       <c r="C63">
-        <v>894590.3001691641</v>
+        <v>878696.0718202207</v>
       </c>
       <c r="D63">
-        <v>1983591.990169164</v>
+        <v>1986584.351820221</v>
       </c>
       <c r="E63">
-        <v>1071124.79</v>
+        <v>1090011.38</v>
       </c>
       <c r="F63">
-        <v>1152081.99</v>
+        <v>1170968.58</v>
       </c>
       <c r="G63">
         <v>63080.3</v>
@@ -6459,28 +6459,28 @@
         <v>207730.1</v>
       </c>
       <c r="M63">
-        <v>63710.134047</v>
+        <v>64754.56247400001</v>
       </c>
       <c r="N63">
-        <v>144019.965953</v>
+        <v>142975.537526</v>
       </c>
       <c r="O63">
-        <v>28803.9931906</v>
+        <v>28595.1075052</v>
       </c>
       <c r="P63">
-        <v>115215.9727624</v>
+        <v>114380.4300208</v>
       </c>
       <c r="Q63">
-        <v>142213.4727624</v>
+        <v>141377.9300208</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.153782181328682</v>
+        <v>0.1563713716254974</v>
       </c>
       <c r="T63">
-        <v>2.104773701224427</v>
+        <v>2.155241839366723</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.260550352111238</v>
+        <v>3.207960830302992</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.086849921217689</v>
+        <v>0.08673839171719198</v>
       </c>
       <c r="C64">
-        <v>878696.0718202207</v>
+        <v>862810.8854079943</v>
       </c>
       <c r="D64">
-        <v>1986584.351820221</v>
+        <v>1989585.755407994</v>
       </c>
       <c r="E64">
-        <v>1090011.38</v>
+        <v>1108897.97</v>
       </c>
       <c r="F64">
-        <v>1170968.58</v>
+        <v>1189855.17</v>
       </c>
       <c r="G64">
         <v>63080.3</v>
@@ -6541,28 +6541,28 @@
         <v>207730.1</v>
       </c>
       <c r="M64">
-        <v>64754.56247400001</v>
+        <v>65798.990901</v>
       </c>
       <c r="N64">
-        <v>142975.537526</v>
+        <v>141931.109099</v>
       </c>
       <c r="O64">
-        <v>28595.1075052</v>
+        <v>28386.2218198</v>
       </c>
       <c r="P64">
-        <v>114380.4300208</v>
+        <v>113544.8872792</v>
       </c>
       <c r="Q64">
-        <v>141377.9300208</v>
+        <v>140542.3872792</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1563713716254974</v>
+        <v>0.1591005181545729</v>
       </c>
       <c r="T64">
-        <v>2.155241839366723</v>
+        <v>2.208437984976169</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.207960830302992</v>
+        <v>3.157040817123579</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08673839171719198</v>
+        <v>0.08662686221669498</v>
       </c>
       <c r="C65">
-        <v>862810.8854079943</v>
+        <v>846934.7819771511</v>
       </c>
       <c r="D65">
-        <v>1989585.755407994</v>
+        <v>1992596.241977151</v>
       </c>
       <c r="E65">
-        <v>1108897.97</v>
+        <v>1127784.56</v>
       </c>
       <c r="F65">
-        <v>1189855.17</v>
+        <v>1208741.76</v>
       </c>
       <c r="G65">
         <v>63080.3</v>
@@ -6623,28 +6623,28 @@
         <v>207730.1</v>
       </c>
       <c r="M65">
-        <v>65798.990901</v>
+        <v>66843.419328</v>
       </c>
       <c r="N65">
-        <v>141931.109099</v>
+        <v>140886.680672</v>
       </c>
       <c r="O65">
-        <v>28386.2218198</v>
+        <v>28177.3361344</v>
       </c>
       <c r="P65">
-        <v>113544.8872792</v>
+        <v>112709.3445376</v>
       </c>
       <c r="Q65">
-        <v>140542.3872792</v>
+        <v>139706.8445376</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1591005181545729</v>
+        <v>0.1619812839352638</v>
       </c>
       <c r="T65">
-        <v>2.208437984976169</v>
+        <v>2.264589472008363</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.157040817123579</v>
+        <v>3.107712054356023</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08662686221669498</v>
+        <v>0.08651533271619798</v>
       </c>
       <c r="C66">
-        <v>846934.7819771511</v>
+        <v>831067.8028211601</v>
       </c>
       <c r="D66">
-        <v>1992596.241977151</v>
+        <v>1995615.85282116</v>
       </c>
       <c r="E66">
-        <v>1127784.56</v>
+        <v>1146671.15</v>
       </c>
       <c r="F66">
-        <v>1208741.76</v>
+        <v>1227628.35</v>
       </c>
       <c r="G66">
         <v>63080.3</v>
@@ -6705,28 +6705,28 @@
         <v>207730.1</v>
       </c>
       <c r="M66">
-        <v>66843.419328</v>
+        <v>67887.84775500001</v>
       </c>
       <c r="N66">
-        <v>140886.680672</v>
+        <v>139842.252245</v>
       </c>
       <c r="O66">
-        <v>28177.3361344</v>
+        <v>27968.450449</v>
       </c>
       <c r="P66">
-        <v>112709.3445376</v>
+        <v>111873.801796</v>
       </c>
       <c r="Q66">
-        <v>139706.8445376</v>
+        <v>138871.301796</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1619812839352638</v>
+        <v>0.1650266649034228</v>
       </c>
       <c r="T66">
-        <v>2.264589472008363</v>
+        <v>2.323949615442396</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.107712054356023</v>
+        <v>3.059901099673623</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08651533271619798</v>
+        <v>0.08640380321570097</v>
       </c>
       <c r="C67">
-        <v>831067.8028211601</v>
+        <v>815209.9894841742</v>
       </c>
       <c r="D67">
-        <v>1995615.85282116</v>
+        <v>1998644.629484174</v>
       </c>
       <c r="E67">
-        <v>1146671.15</v>
+        <v>1165557.74</v>
       </c>
       <c r="F67">
-        <v>1227628.35</v>
+        <v>1246514.94</v>
       </c>
       <c r="G67">
         <v>63080.3</v>
@@ -6787,28 +6787,28 @@
         <v>207730.1</v>
       </c>
       <c r="M67">
-        <v>67887.84775500001</v>
+        <v>68932.276182</v>
       </c>
       <c r="N67">
-        <v>139842.252245</v>
+        <v>138797.823818</v>
       </c>
       <c r="O67">
-        <v>27968.450449</v>
+        <v>27759.5647636</v>
       </c>
       <c r="P67">
-        <v>111873.801796</v>
+        <v>111038.2590544</v>
       </c>
       <c r="Q67">
-        <v>138871.301796</v>
+        <v>138035.7590544</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1650266649034228</v>
+        <v>0.1682511859285323</v>
       </c>
       <c r="T67">
-        <v>2.323949615442396</v>
+        <v>2.386801532019607</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.059901099673623</v>
+        <v>3.01353896179978</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08640380321570097</v>
+        <v>0.08763227371520396</v>
       </c>
       <c r="C68">
-        <v>815209.9894841742</v>
+        <v>763460.8947719142</v>
       </c>
       <c r="D68">
-        <v>1998644.629484174</v>
+        <v>1965782.124771914</v>
       </c>
       <c r="E68">
-        <v>1165557.74</v>
+        <v>1184444.33</v>
       </c>
       <c r="F68">
-        <v>1246514.94</v>
+        <v>1265401.53</v>
       </c>
       <c r="G68">
         <v>63080.3</v>
@@ -6869,45 +6869,45 @@
         <v>207730.1</v>
       </c>
       <c r="M68">
-        <v>68932.276182</v>
+        <v>73140.208434</v>
       </c>
       <c r="N68">
-        <v>138797.823818</v>
+        <v>134589.891566</v>
       </c>
       <c r="O68">
-        <v>27759.5647636</v>
+        <v>26917.9783132</v>
       </c>
       <c r="P68">
-        <v>111038.2590544</v>
+        <v>107671.9132528</v>
       </c>
       <c r="Q68">
-        <v>138035.7590544</v>
+        <v>134669.4132528</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1682511859285323</v>
+        <v>0.1716711324703151</v>
       </c>
       <c r="T68">
-        <v>2.386801532019607</v>
+        <v>2.453462655662105</v>
       </c>
       <c r="U68">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V68">
         <v>0.2</v>
       </c>
       <c r="W68">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y68">
-        <v>3.01353896179978</v>
+        <v>2.840162811231947</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08763227371520396</v>
+        <v>0.08754074421470695</v>
       </c>
       <c r="C69">
-        <v>763460.8947719142</v>
+        <v>746985.4823174679</v>
       </c>
       <c r="D69">
-        <v>1965782.124771914</v>
+        <v>1968193.302317468</v>
       </c>
       <c r="E69">
-        <v>1184444.33</v>
+        <v>1203330.92</v>
       </c>
       <c r="F69">
-        <v>1265401.53</v>
+        <v>1284288.12</v>
       </c>
       <c r="G69">
         <v>63080.3</v>
@@ -6951,28 +6951,28 @@
         <v>207730.1</v>
       </c>
       <c r="M69">
-        <v>73140.208434</v>
+        <v>74231.85333600001</v>
       </c>
       <c r="N69">
-        <v>134589.891566</v>
+        <v>133498.246664</v>
       </c>
       <c r="O69">
-        <v>26917.9783132</v>
+        <v>26699.6493328</v>
       </c>
       <c r="P69">
-        <v>107671.9132528</v>
+        <v>106798.5973312</v>
       </c>
       <c r="Q69">
-        <v>134669.4132528</v>
+        <v>133796.0973312</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1716711324703151</v>
+        <v>0.1753048256709592</v>
       </c>
       <c r="T69">
-        <v>2.453462655662105</v>
+        <v>2.524290099532257</v>
       </c>
       <c r="U69">
         <v>0.0578</v>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.840162811231947</v>
+        <v>2.798395711066771</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08754074421470695</v>
+        <v>0.08744921471420995</v>
       </c>
       <c r="C70">
-        <v>746985.4823174679</v>
+        <v>730515.9921032016</v>
       </c>
       <c r="D70">
-        <v>1968193.302317468</v>
+        <v>1970610.402103202</v>
       </c>
       <c r="E70">
-        <v>1203330.92</v>
+        <v>1222217.51</v>
       </c>
       <c r="F70">
-        <v>1284288.12</v>
+        <v>1303174.71</v>
       </c>
       <c r="G70">
         <v>63080.3</v>
@@ -7033,28 +7033,28 @@
         <v>207730.1</v>
       </c>
       <c r="M70">
-        <v>74231.85333600001</v>
+        <v>75323.49823800001</v>
       </c>
       <c r="N70">
-        <v>133498.246664</v>
+        <v>132406.601762</v>
       </c>
       <c r="O70">
-        <v>26699.6493328</v>
+        <v>26481.3203524</v>
       </c>
       <c r="P70">
-        <v>106798.5973312</v>
+        <v>105925.2814096</v>
       </c>
       <c r="Q70">
-        <v>133796.0973312</v>
+        <v>132922.7814096</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1753048256709592</v>
+        <v>0.1791729506909999</v>
       </c>
       <c r="T70">
-        <v>2.524290099532257</v>
+        <v>2.599687055910163</v>
       </c>
       <c r="U70">
         <v>0.0578</v>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.798395711066771</v>
+        <v>2.757839251486093</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08744921471420995</v>
+        <v>0.08735768521371294</v>
       </c>
       <c r="C71">
-        <v>730515.9921032016</v>
+        <v>714052.4459749074</v>
       </c>
       <c r="D71">
-        <v>1970610.402103202</v>
+        <v>1973033.445974907</v>
       </c>
       <c r="E71">
-        <v>1222217.51</v>
+        <v>1241104.1</v>
       </c>
       <c r="F71">
-        <v>1303174.71</v>
+        <v>1322061.3</v>
       </c>
       <c r="G71">
         <v>63080.3</v>
@@ -7115,28 +7115,28 @@
         <v>207730.1</v>
       </c>
       <c r="M71">
-        <v>75323.49823800001</v>
+        <v>76415.14314000001</v>
       </c>
       <c r="N71">
-        <v>132406.601762</v>
+        <v>131314.95686</v>
       </c>
       <c r="O71">
-        <v>26481.3203524</v>
+        <v>26262.991372</v>
       </c>
       <c r="P71">
-        <v>105925.2814096</v>
+        <v>105051.965488</v>
       </c>
       <c r="Q71">
-        <v>132922.7814096</v>
+        <v>132049.465488</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1791729506909999</v>
+        <v>0.1832989507123765</v>
       </c>
       <c r="T71">
-        <v>2.599687055910163</v>
+        <v>2.680110476046594</v>
       </c>
       <c r="U71">
         <v>0.0578</v>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.757839251486093</v>
+        <v>2.718441547893434</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08735768521371294</v>
+        <v>0.08726615571321594</v>
       </c>
       <c r="C72">
-        <v>714052.4459749074</v>
+        <v>697594.8658859527</v>
       </c>
       <c r="D72">
-        <v>1973033.445974907</v>
+        <v>1975462.455885953</v>
       </c>
       <c r="E72">
-        <v>1241104.1</v>
+        <v>1259990.69</v>
       </c>
       <c r="F72">
-        <v>1322061.3</v>
+        <v>1340947.89</v>
       </c>
       <c r="G72">
         <v>63080.3</v>
@@ -7197,28 +7197,28 @@
         <v>207730.1</v>
       </c>
       <c r="M72">
-        <v>76415.14314000001</v>
+        <v>77506.78804200001</v>
       </c>
       <c r="N72">
-        <v>131314.95686</v>
+        <v>130223.311958</v>
       </c>
       <c r="O72">
-        <v>26262.991372</v>
+        <v>26044.6623916</v>
       </c>
       <c r="P72">
-        <v>105051.965488</v>
+        <v>104178.6495664</v>
       </c>
       <c r="Q72">
-        <v>132049.465488</v>
+        <v>131176.1495664</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1832989507123765</v>
+        <v>0.1877095024593654</v>
       </c>
       <c r="T72">
-        <v>2.680110476046594</v>
+        <v>2.766080338951057</v>
       </c>
       <c r="U72">
         <v>0.0578</v>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.718441547893434</v>
+        <v>2.680153638768175</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08726615571321594</v>
+        <v>0.08717462621271893</v>
       </c>
       <c r="C73">
-        <v>697594.865885953</v>
+        <v>681143.2738979491</v>
       </c>
       <c r="D73">
-        <v>1975462.455885953</v>
+        <v>1977897.453897949</v>
       </c>
       <c r="E73">
-        <v>1259990.69</v>
+        <v>1278877.28</v>
       </c>
       <c r="F73">
-        <v>1340947.89</v>
+        <v>1359834.48</v>
       </c>
       <c r="G73">
         <v>63080.3</v>
@@ -7279,28 +7279,28 @@
         <v>207730.1</v>
       </c>
       <c r="M73">
-        <v>77506.788042</v>
+        <v>78598.432944</v>
       </c>
       <c r="N73">
-        <v>130223.311958</v>
+        <v>129131.667056</v>
       </c>
       <c r="O73">
-        <v>26044.6623916</v>
+        <v>25826.3334112</v>
       </c>
       <c r="P73">
-        <v>104178.6495664</v>
+        <v>103305.3336448</v>
       </c>
       <c r="Q73">
-        <v>131176.1495664</v>
+        <v>130302.8336448</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1877095024593653</v>
+        <v>0.1924350936168533</v>
       </c>
       <c r="T73">
-        <v>2.766080338951055</v>
+        <v>2.858190906348693</v>
       </c>
       <c r="U73">
         <v>0.0578</v>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.680153638768175</v>
+        <v>2.642929282674173</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08717462621271893</v>
+        <v>0.08708309671222192</v>
       </c>
       <c r="C74">
-        <v>681143.2738979491</v>
+        <v>664697.6921814138</v>
       </c>
       <c r="D74">
-        <v>1977897.453897949</v>
+        <v>1980338.462181414</v>
       </c>
       <c r="E74">
-        <v>1278877.28</v>
+        <v>1297763.87</v>
       </c>
       <c r="F74">
-        <v>1359834.48</v>
+        <v>1378721.07</v>
       </c>
       <c r="G74">
         <v>63080.3</v>
@@ -7361,28 +7361,28 @@
         <v>207730.1</v>
       </c>
       <c r="M74">
-        <v>78598.432944</v>
+        <v>79690.07784600001</v>
       </c>
       <c r="N74">
-        <v>129131.667056</v>
+        <v>128040.022154</v>
       </c>
       <c r="O74">
-        <v>25826.3334112</v>
+        <v>25608.0044308</v>
       </c>
       <c r="P74">
-        <v>103305.3336448</v>
+        <v>102432.0177232</v>
       </c>
       <c r="Q74">
-        <v>130302.8336448</v>
+        <v>129429.5177232</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1924350936168533</v>
+        <v>0.1975107285637849</v>
       </c>
       <c r="T74">
-        <v>2.858190906348693</v>
+        <v>2.957124478738748</v>
       </c>
       <c r="U74">
         <v>0.0578</v>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.642929282674173</v>
+        <v>2.606724771952608</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08708309671222192</v>
+        <v>0.08699156721172491</v>
       </c>
       <c r="C75">
-        <v>664697.6921814138</v>
+        <v>648258.1430164473</v>
       </c>
       <c r="D75">
-        <v>1980338.462181414</v>
+        <v>1982785.503016447</v>
       </c>
       <c r="E75">
-        <v>1297763.87</v>
+        <v>1316650.46</v>
       </c>
       <c r="F75">
-        <v>1378721.07</v>
+        <v>1397607.66</v>
       </c>
       <c r="G75">
         <v>63080.3</v>
@@ -7443,28 +7443,28 @@
         <v>207730.1</v>
       </c>
       <c r="M75">
-        <v>79690.07784600001</v>
+        <v>80781.722748</v>
       </c>
       <c r="N75">
-        <v>128040.022154</v>
+        <v>126948.377252</v>
       </c>
       <c r="O75">
-        <v>25608.0044308</v>
+        <v>25389.6754504</v>
       </c>
       <c r="P75">
-        <v>102432.0177232</v>
+        <v>101558.7018016</v>
       </c>
       <c r="Q75">
-        <v>129429.5177232</v>
+        <v>128556.2018016</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1975107285637849</v>
+        <v>0.2029767969681727</v>
       </c>
       <c r="T75">
-        <v>2.957124478738748</v>
+        <v>3.063668325928038</v>
       </c>
       <c r="U75">
         <v>0.0578</v>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.606724771952608</v>
+        <v>2.571498761520817</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.08699156721172491</v>
+        <v>0.08690003771122792</v>
       </c>
       <c r="C76">
-        <v>648258.1430164473</v>
+        <v>631824.6487934082</v>
       </c>
       <c r="D76">
-        <v>1982785.503016447</v>
+        <v>1985238.598793408</v>
       </c>
       <c r="E76">
-        <v>1316650.46</v>
+        <v>1335537.05</v>
       </c>
       <c r="F76">
-        <v>1397607.66</v>
+        <v>1416494.25</v>
       </c>
       <c r="G76">
         <v>63080.3</v>
@@ -7525,28 +7525,28 @@
         <v>207730.1</v>
       </c>
       <c r="M76">
-        <v>80781.722748</v>
+        <v>81873.36765</v>
       </c>
       <c r="N76">
-        <v>126948.377252</v>
+        <v>125856.73235</v>
       </c>
       <c r="O76">
-        <v>25389.6754504</v>
+        <v>25171.34647</v>
       </c>
       <c r="P76">
-        <v>101558.7018016</v>
+        <v>100685.38588</v>
       </c>
       <c r="Q76">
-        <v>128556.2018016</v>
+        <v>127682.88588</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2029767969681727</v>
+        <v>0.2088801508449117</v>
       </c>
       <c r="T76">
-        <v>3.063668325928038</v>
+        <v>3.178735680892472</v>
       </c>
       <c r="U76">
         <v>0.0578</v>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.571498761520817</v>
+        <v>2.537212111367206</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.08690003771122792</v>
+        <v>0.08680850821073091</v>
       </c>
       <c r="C77">
-        <v>631824.6487934082</v>
+        <v>615397.2320135997</v>
       </c>
       <c r="D77">
-        <v>1985238.598793408</v>
+        <v>1987697.7720136</v>
       </c>
       <c r="E77">
-        <v>1335537.05</v>
+        <v>1354423.64</v>
       </c>
       <c r="F77">
-        <v>1416494.25</v>
+        <v>1435380.84</v>
       </c>
       <c r="G77">
         <v>63080.3</v>
@@ -7607,28 +7607,28 @@
         <v>207730.1</v>
       </c>
       <c r="M77">
-        <v>81873.36765</v>
+        <v>82965.01255200001</v>
       </c>
       <c r="N77">
-        <v>125856.73235</v>
+        <v>124765.087448</v>
       </c>
       <c r="O77">
-        <v>25171.34647</v>
+        <v>24953.0174896</v>
       </c>
       <c r="P77">
-        <v>100685.38588</v>
+        <v>99812.0699584</v>
       </c>
       <c r="Q77">
-        <v>127682.88588</v>
+        <v>126809.5699584</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2088801508449117</v>
+        <v>0.2152754508780454</v>
       </c>
       <c r="T77">
-        <v>3.178735680892472</v>
+        <v>3.303391982103942</v>
       </c>
       <c r="U77">
         <v>0.0578</v>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.537212111367206</v>
+        <v>2.503827741480795</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08680850821073091</v>
+        <v>0.08887297871023389</v>
       </c>
       <c r="C78">
-        <v>615397.2320135997</v>
+        <v>542484.1649017832</v>
       </c>
       <c r="D78">
-        <v>1987697.7720136</v>
+        <v>1933671.294901783</v>
       </c>
       <c r="E78">
-        <v>1354423.64</v>
+        <v>1373310.23</v>
       </c>
       <c r="F78">
-        <v>1435380.84</v>
+        <v>1454267.43</v>
       </c>
       <c r="G78">
         <v>63080.3</v>
@@ -7689,45 +7689,45 @@
         <v>207730.1</v>
       </c>
       <c r="M78">
-        <v>82965.01255200001</v>
+        <v>89146.593459</v>
       </c>
       <c r="N78">
-        <v>124765.087448</v>
+        <v>118583.506541</v>
       </c>
       <c r="O78">
-        <v>24953.0174896</v>
+        <v>23716.7013082</v>
       </c>
       <c r="P78">
-        <v>99812.0699584</v>
+        <v>94866.8052328</v>
       </c>
       <c r="Q78">
-        <v>126809.5699584</v>
+        <v>121864.3052328</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2152754508780454</v>
+        <v>0.2222268639575387</v>
       </c>
       <c r="T78">
-        <v>3.303391982103942</v>
+        <v>3.438887961681626</v>
       </c>
       <c r="U78">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V78">
         <v>0.2</v>
       </c>
       <c r="W78">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y78">
-        <v>2.503827741480795</v>
+        <v>2.330207941098036</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.08887297871023389</v>
+        <v>0.08880944920973688</v>
       </c>
       <c r="C79">
-        <v>542484.1649017832</v>
+        <v>525216.2851327572</v>
       </c>
       <c r="D79">
-        <v>1933671.294901783</v>
+        <v>1935290.005132757</v>
       </c>
       <c r="E79">
-        <v>1373310.23</v>
+        <v>1392196.82</v>
       </c>
       <c r="F79">
-        <v>1454267.43</v>
+        <v>1473154.02</v>
       </c>
       <c r="G79">
         <v>63080.3</v>
@@ -7771,28 +7771,28 @@
         <v>207730.1</v>
       </c>
       <c r="M79">
-        <v>89146.593459</v>
+        <v>90304.341426</v>
       </c>
       <c r="N79">
-        <v>118583.506541</v>
+        <v>117425.758574</v>
       </c>
       <c r="O79">
-        <v>23716.7013082</v>
+        <v>23485.1517148</v>
       </c>
       <c r="P79">
-        <v>94866.8052328</v>
+        <v>93940.60685920001</v>
       </c>
       <c r="Q79">
-        <v>121864.3052328</v>
+        <v>120938.1068592</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2222268639575387</v>
+        <v>0.2298102236806222</v>
       </c>
       <c r="T79">
-        <v>3.438887961681626</v>
+        <v>3.586701757584554</v>
       </c>
       <c r="U79">
         <v>0.0613</v>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.330207941098036</v>
+        <v>2.300333480314728</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.08880944920973688</v>
+        <v>0.08874591970923988</v>
       </c>
       <c r="C80">
-        <v>525216.2851327572</v>
+        <v>507951.1177358818</v>
       </c>
       <c r="D80">
-        <v>1935290.005132757</v>
+        <v>1936911.427735882</v>
       </c>
       <c r="E80">
-        <v>1392196.82</v>
+        <v>1411083.41</v>
       </c>
       <c r="F80">
-        <v>1473154.02</v>
+        <v>1492040.61</v>
       </c>
       <c r="G80">
         <v>63080.3</v>
@@ -7853,28 +7853,28 @@
         <v>207730.1</v>
       </c>
       <c r="M80">
-        <v>90304.341426</v>
+        <v>91462.089393</v>
       </c>
       <c r="N80">
-        <v>117425.758574</v>
+        <v>116268.010607</v>
       </c>
       <c r="O80">
-        <v>23485.1517148</v>
+        <v>23253.6021214</v>
       </c>
       <c r="P80">
-        <v>93940.60685920001</v>
+        <v>93014.4084856</v>
       </c>
       <c r="Q80">
-        <v>120938.1068592</v>
+        <v>120011.9084856</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2298102236806222</v>
+        <v>0.2381158081392376</v>
       </c>
       <c r="T80">
-        <v>3.586701757584554</v>
+        <v>3.74859305785919</v>
       </c>
       <c r="U80">
         <v>0.0613</v>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.300333480314728</v>
+        <v>2.271215334994288</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.08874591970923988</v>
+        <v>0.09047439020874287</v>
       </c>
       <c r="C81">
-        <v>507951.1177358818</v>
+        <v>445896.9251304718</v>
       </c>
       <c r="D81">
-        <v>1936911.427735882</v>
+        <v>1893743.825130472</v>
       </c>
       <c r="E81">
-        <v>1411083.41</v>
+        <v>1429970</v>
       </c>
       <c r="F81">
-        <v>1492040.61</v>
+        <v>1510927.2</v>
       </c>
       <c r="G81">
         <v>63080.3</v>
@@ -7935,45 +7935,45 @@
         <v>207730.1</v>
       </c>
       <c r="M81">
-        <v>91462.089393</v>
+        <v>96850.43352000002</v>
       </c>
       <c r="N81">
-        <v>116268.010607</v>
+        <v>110879.66648</v>
       </c>
       <c r="O81">
-        <v>23253.6021214</v>
+        <v>22175.933296</v>
       </c>
       <c r="P81">
-        <v>93014.4084856</v>
+        <v>88703.73318399998</v>
       </c>
       <c r="Q81">
-        <v>120011.9084856</v>
+        <v>115701.233184</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2381158081392376</v>
+        <v>0.2472519510437144</v>
       </c>
       <c r="T81">
-        <v>3.74859305785919</v>
+        <v>3.92667348816129</v>
       </c>
       <c r="U81">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V81">
         <v>0.2</v>
       </c>
       <c r="W81">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y81">
-        <v>2.271215334994288</v>
+        <v>2.144854622226372</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09047439020874287</v>
+        <v>0.09043326070824587</v>
       </c>
       <c r="C82">
-        <v>445896.9251304718</v>
+        <v>428015.1619976342</v>
       </c>
       <c r="D82">
-        <v>1893743.825130472</v>
+        <v>1894748.651997634</v>
       </c>
       <c r="E82">
-        <v>1429970</v>
+        <v>1448856.59</v>
       </c>
       <c r="F82">
-        <v>1510927.2</v>
+        <v>1529813.79</v>
       </c>
       <c r="G82">
         <v>63080.3</v>
@@ -8017,28 +8017,28 @@
         <v>207730.1</v>
       </c>
       <c r="M82">
-        <v>96850.43352000002</v>
+        <v>98061.06393900001</v>
       </c>
       <c r="N82">
-        <v>110879.66648</v>
+        <v>109669.036061</v>
       </c>
       <c r="O82">
-        <v>22175.933296</v>
+        <v>21933.8072122</v>
       </c>
       <c r="P82">
-        <v>88703.73318399998</v>
+        <v>87735.22884879999</v>
       </c>
       <c r="Q82">
-        <v>115701.233184</v>
+        <v>114732.7288488</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2472519510437144</v>
+        <v>0.2573497932012941</v>
       </c>
       <c r="T82">
-        <v>3.92667348816129</v>
+        <v>4.123499226916242</v>
       </c>
       <c r="U82">
         <v>0.0641</v>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.144854622226372</v>
+        <v>2.118374935532219</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09043326070824587</v>
+        <v>0.09039213120774885</v>
       </c>
       <c r="C83">
-        <v>428015.1619976342</v>
+        <v>410134.4657599512</v>
       </c>
       <c r="D83">
-        <v>1894748.651997634</v>
+        <v>1895754.545759951</v>
       </c>
       <c r="E83">
-        <v>1448856.59</v>
+        <v>1467743.18</v>
       </c>
       <c r="F83">
-        <v>1529813.79</v>
+        <v>1548700.38</v>
       </c>
       <c r="G83">
         <v>63080.3</v>
@@ -8099,28 +8099,28 @@
         <v>207730.1</v>
       </c>
       <c r="M83">
-        <v>98061.06393900001</v>
+        <v>99271.69435800001</v>
       </c>
       <c r="N83">
-        <v>109669.036061</v>
+        <v>108458.405642</v>
       </c>
       <c r="O83">
-        <v>21933.8072122</v>
+        <v>21691.6811284</v>
       </c>
       <c r="P83">
-        <v>87735.22884879999</v>
+        <v>86766.7245136</v>
       </c>
       <c r="Q83">
-        <v>114732.7288488</v>
+        <v>113764.2245136</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2573497932012941</v>
+        <v>0.268569617820827</v>
       </c>
       <c r="T83">
-        <v>4.123499226916242</v>
+        <v>4.342194492199521</v>
       </c>
       <c r="U83">
         <v>0.0641</v>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.118374935532219</v>
+        <v>2.092541094854997</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09039213120774885</v>
+        <v>0.09035100170725185</v>
       </c>
       <c r="C84">
-        <v>410134.4657599512</v>
+        <v>392254.8381175206</v>
       </c>
       <c r="D84">
-        <v>1895754.545759951</v>
+        <v>1896761.508117521</v>
       </c>
       <c r="E84">
-        <v>1467743.18</v>
+        <v>1486629.77</v>
       </c>
       <c r="F84">
-        <v>1548700.38</v>
+        <v>1567586.97</v>
       </c>
       <c r="G84">
         <v>63080.3</v>
@@ -8181,28 +8181,28 @@
         <v>207730.1</v>
       </c>
       <c r="M84">
-        <v>99271.69435800001</v>
+        <v>100482.324777</v>
       </c>
       <c r="N84">
-        <v>108458.405642</v>
+        <v>107247.775223</v>
       </c>
       <c r="O84">
-        <v>21691.6811284</v>
+        <v>21449.5550446</v>
       </c>
       <c r="P84">
-        <v>86766.7245136</v>
+        <v>85798.22017839999</v>
       </c>
       <c r="Q84">
-        <v>113764.2245136</v>
+        <v>112795.7201784</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.268569617820827</v>
+        <v>0.2811094218073639</v>
       </c>
       <c r="T84">
-        <v>4.342194492199521</v>
+        <v>4.586618612222011</v>
       </c>
       <c r="U84">
         <v>0.0641</v>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.092541094854997</v>
+        <v>2.067329756362768</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.09035100170725185</v>
+        <v>0.09030987220675485</v>
       </c>
       <c r="C85">
-        <v>392254.8381175206</v>
+        <v>374376.2807740562</v>
       </c>
       <c r="D85">
-        <v>1896761.508117521</v>
+        <v>1897769.540774056</v>
       </c>
       <c r="E85">
-        <v>1486629.77</v>
+        <v>1505516.36</v>
       </c>
       <c r="F85">
-        <v>1567586.97</v>
+        <v>1586473.56</v>
       </c>
       <c r="G85">
         <v>63080.3</v>
@@ -8263,28 +8263,28 @@
         <v>207730.1</v>
       </c>
       <c r="M85">
-        <v>100482.324777</v>
+        <v>101692.955196</v>
       </c>
       <c r="N85">
-        <v>107247.775223</v>
+        <v>106037.144804</v>
       </c>
       <c r="O85">
-        <v>21449.5550446</v>
+        <v>21207.4289608</v>
       </c>
       <c r="P85">
-        <v>85798.22017839999</v>
+        <v>84829.7158432</v>
       </c>
       <c r="Q85">
-        <v>112795.7201784</v>
+        <v>111827.2158432</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2811094218073639</v>
+        <v>0.2952167012922179</v>
       </c>
       <c r="T85">
-        <v>4.586618612222011</v>
+        <v>4.861595747247312</v>
       </c>
       <c r="U85">
         <v>0.0641</v>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.067329756362768</v>
+        <v>2.042718687834641</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.09030987220675485</v>
+        <v>0.09026874270625784</v>
       </c>
       <c r="C86">
-        <v>374376.2807740562</v>
+        <v>356498.7954368943</v>
       </c>
       <c r="D86">
-        <v>1897769.540774056</v>
+        <v>1898778.645436894</v>
       </c>
       <c r="E86">
-        <v>1505516.36</v>
+        <v>1524402.95</v>
       </c>
       <c r="F86">
-        <v>1586473.56</v>
+        <v>1605360.15</v>
       </c>
       <c r="G86">
         <v>63080.3</v>
@@ -8345,28 +8345,28 @@
         <v>207730.1</v>
       </c>
       <c r="M86">
-        <v>101692.955196</v>
+        <v>102903.585615</v>
       </c>
       <c r="N86">
-        <v>106037.144804</v>
+        <v>104826.514385</v>
       </c>
       <c r="O86">
-        <v>21207.4289608</v>
+        <v>20965.302877</v>
       </c>
       <c r="P86">
-        <v>84829.7158432</v>
+        <v>83861.21150800001</v>
       </c>
       <c r="Q86">
-        <v>111827.2158432</v>
+        <v>110858.711508</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2952167012922177</v>
+        <v>0.3112049513750522</v>
       </c>
       <c r="T86">
-        <v>4.861595747247309</v>
+        <v>5.173236500275983</v>
       </c>
       <c r="U86">
         <v>0.0641</v>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.042718687834641</v>
+        <v>2.01868670327188</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.09026874270625784</v>
+        <v>0.09559401320576083</v>
       </c>
       <c r="C87">
-        <v>356498.7954368943</v>
+        <v>215308.381676743</v>
       </c>
       <c r="D87">
-        <v>1898778.645436894</v>
+        <v>1776474.821676743</v>
       </c>
       <c r="E87">
-        <v>1524402.95</v>
+        <v>1543289.54</v>
       </c>
       <c r="F87">
-        <v>1605360.15</v>
+        <v>1624246.74</v>
       </c>
       <c r="G87">
         <v>63080.3</v>
@@ -8427,45 +8427,45 @@
         <v>207730.1</v>
       </c>
       <c r="M87">
-        <v>102903.585615</v>
+        <v>116783.340606</v>
       </c>
       <c r="N87">
-        <v>104826.514385</v>
+        <v>90946.75939399999</v>
       </c>
       <c r="O87">
-        <v>20965.302877</v>
+        <v>18189.3518788</v>
       </c>
       <c r="P87">
-        <v>83861.21150800001</v>
+        <v>72757.4075152</v>
       </c>
       <c r="Q87">
-        <v>110858.711508</v>
+        <v>99754.9075152</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3112049513750522</v>
+        <v>0.3294772371840059</v>
       </c>
       <c r="T87">
-        <v>5.173236500275983</v>
+        <v>5.529397360880182</v>
       </c>
       <c r="U87">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V87">
         <v>0.2</v>
       </c>
       <c r="W87">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y87">
-        <v>2.01868670327188</v>
+        <v>1.778764838564032</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.09559401320576083</v>
+        <v>0.09561528370526383</v>
       </c>
       <c r="C88">
-        <v>215308.381676743</v>
+        <v>195964.8623330803</v>
       </c>
       <c r="D88">
-        <v>1776474.821676743</v>
+        <v>1776017.89233308</v>
       </c>
       <c r="E88">
-        <v>1543289.54</v>
+        <v>1562176.13</v>
       </c>
       <c r="F88">
-        <v>1624246.74</v>
+        <v>1643133.33</v>
       </c>
       <c r="G88">
         <v>63080.3</v>
@@ -8509,28 +8509,28 @@
         <v>207730.1</v>
       </c>
       <c r="M88">
-        <v>116783.340606</v>
+        <v>118141.286427</v>
       </c>
       <c r="N88">
-        <v>90946.75939399999</v>
+        <v>89588.81357299999</v>
       </c>
       <c r="O88">
-        <v>18189.3518788</v>
+        <v>17917.7627146</v>
       </c>
       <c r="P88">
-        <v>72757.4075152</v>
+        <v>71671.05085839999</v>
       </c>
       <c r="Q88">
-        <v>99754.9075152</v>
+        <v>98668.55085839999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3294772371840059</v>
+        <v>0.3505606438866448</v>
       </c>
       <c r="T88">
-        <v>5.529397360880182</v>
+        <v>5.940352200038872</v>
       </c>
       <c r="U88">
         <v>0.07190000000000001</v>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>1.778764838564032</v>
+        <v>1.758319265706974</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.09561528370526383</v>
+        <v>0.09838215420476681</v>
       </c>
       <c r="C89">
-        <v>195964.8623330803</v>
+        <v>119579.8929107564</v>
       </c>
       <c r="D89">
-        <v>1776017.89233308</v>
+        <v>1718519.512910756</v>
       </c>
       <c r="E89">
-        <v>1562176.13</v>
+        <v>1581062.72</v>
       </c>
       <c r="F89">
-        <v>1643133.33</v>
+        <v>1662019.92</v>
       </c>
       <c r="G89">
         <v>63080.3</v>
@@ -8591,45 +8591,45 @@
         <v>207730.1</v>
       </c>
       <c r="M89">
-        <v>118141.286427</v>
+        <v>125981.109936</v>
       </c>
       <c r="N89">
-        <v>89588.81357299999</v>
+        <v>81748.990064</v>
       </c>
       <c r="O89">
-        <v>17917.7627146</v>
+        <v>16349.7980128</v>
       </c>
       <c r="P89">
-        <v>71671.05085839999</v>
+        <v>65399.1920512</v>
       </c>
       <c r="Q89">
-        <v>98668.55085839999</v>
+        <v>92396.69205119999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3505606438866448</v>
+        <v>0.3751579517063902</v>
       </c>
       <c r="T89">
-        <v>5.940352200038872</v>
+        <v>6.419799512390679</v>
       </c>
       <c r="U89">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V89">
         <v>0.2</v>
       </c>
       <c r="W89">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y89">
-        <v>1.758319265706974</v>
+        <v>1.648898792092953</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.09838215420476681</v>
+        <v>0.09843462470426981</v>
       </c>
       <c r="C90">
-        <v>119579.8929107564</v>
+        <v>99638.86127366847</v>
       </c>
       <c r="D90">
-        <v>1718519.512910756</v>
+        <v>1717465.071273668</v>
       </c>
       <c r="E90">
-        <v>1581062.72</v>
+        <v>1599949.31</v>
       </c>
       <c r="F90">
-        <v>1662019.92</v>
+        <v>1680906.51</v>
       </c>
       <c r="G90">
         <v>63080.3</v>
@@ -8673,28 +8673,28 @@
         <v>207730.1</v>
       </c>
       <c r="M90">
-        <v>125981.109936</v>
+        <v>127412.713458</v>
       </c>
       <c r="N90">
-        <v>81748.990064</v>
+        <v>80317.38654199999</v>
       </c>
       <c r="O90">
-        <v>16349.7980128</v>
+        <v>16063.4773084</v>
       </c>
       <c r="P90">
-        <v>65399.1920512</v>
+        <v>64253.9092336</v>
       </c>
       <c r="Q90">
-        <v>92396.69205119999</v>
+        <v>91251.40923359999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3751579517063902</v>
+        <v>0.4042274973115437</v>
       </c>
       <c r="T90">
-        <v>6.419799512390679</v>
+        <v>6.986419063351904</v>
       </c>
       <c r="U90">
         <v>0.07580000000000001</v>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>1.648898792092953</v>
+        <v>1.630371839372808</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.09843462470426981</v>
+        <v>0.09848709520377281</v>
       </c>
       <c r="C91">
-        <v>99638.86127366847</v>
+        <v>79699.12280244054</v>
       </c>
       <c r="D91">
-        <v>1717465.071273668</v>
+        <v>1716411.922802441</v>
       </c>
       <c r="E91">
-        <v>1599949.31</v>
+        <v>1618835.9</v>
       </c>
       <c r="F91">
-        <v>1680906.51</v>
+        <v>1699793.1</v>
       </c>
       <c r="G91">
         <v>63080.3</v>
@@ -8755,28 +8755,28 @@
         <v>207730.1</v>
       </c>
       <c r="M91">
-        <v>127412.713458</v>
+        <v>128844.31698</v>
       </c>
       <c r="N91">
-        <v>80317.38654199999</v>
+        <v>78885.78301999999</v>
       </c>
       <c r="O91">
-        <v>16063.4773084</v>
+        <v>15777.156604</v>
       </c>
       <c r="P91">
-        <v>64253.9092336</v>
+        <v>63108.62641599999</v>
       </c>
       <c r="Q91">
-        <v>91251.40923359999</v>
+        <v>90106.12641599998</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4042274973115437</v>
+        <v>0.4391109520377282</v>
       </c>
       <c r="T91">
-        <v>6.986419063351904</v>
+        <v>7.666362524505375</v>
       </c>
       <c r="U91">
         <v>0.07580000000000001</v>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>1.630371839372808</v>
+        <v>1.61225659671311</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.09848709520377281</v>
+        <v>0.09853956570327579</v>
       </c>
       <c r="C92">
-        <v>79699.12280244054</v>
+        <v>59760.67511962587</v>
       </c>
       <c r="D92">
-        <v>1716411.922802441</v>
+        <v>1715360.065119626</v>
       </c>
       <c r="E92">
-        <v>1618835.9</v>
+        <v>1637722.49</v>
       </c>
       <c r="F92">
-        <v>1699793.1</v>
+        <v>1718679.69</v>
       </c>
       <c r="G92">
         <v>63080.3</v>
@@ -8837,28 +8837,28 @@
         <v>207730.1</v>
       </c>
       <c r="M92">
-        <v>128844.31698</v>
+        <v>130275.920502</v>
       </c>
       <c r="N92">
-        <v>78885.78301999999</v>
+        <v>77454.179498</v>
       </c>
       <c r="O92">
-        <v>15777.156604</v>
+        <v>15490.8358996</v>
       </c>
       <c r="P92">
-        <v>63108.62641599999</v>
+        <v>61963.3435984</v>
       </c>
       <c r="Q92">
-        <v>90106.12641599998</v>
+        <v>88960.8435984</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4391109520377282</v>
+        <v>0.4817462855919534</v>
       </c>
       <c r="T92">
-        <v>7.666362524505375</v>
+        <v>8.497404532581839</v>
       </c>
       <c r="U92">
         <v>0.07580000000000001</v>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>1.61225659671311</v>
+        <v>1.594539491254724</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.09853956570327579</v>
+        <v>0.09859203620277879</v>
       </c>
       <c r="C93">
-        <v>59760.67511962587</v>
+        <v>39823.51585360011</v>
       </c>
       <c r="D93">
-        <v>1715360.065119626</v>
+        <v>1714309.4958536</v>
       </c>
       <c r="E93">
-        <v>1637722.49</v>
+        <v>1656609.08</v>
       </c>
       <c r="F93">
-        <v>1718679.69</v>
+        <v>1737566.28</v>
       </c>
       <c r="G93">
         <v>63080.3</v>
@@ -8919,28 +8919,28 @@
         <v>207730.1</v>
       </c>
       <c r="M93">
-        <v>130275.920502</v>
+        <v>131707.524024</v>
       </c>
       <c r="N93">
-        <v>77454.179498</v>
+        <v>76022.57597599999</v>
       </c>
       <c r="O93">
-        <v>15490.8358996</v>
+        <v>15204.5151952</v>
       </c>
       <c r="P93">
-        <v>61963.3435984</v>
+        <v>60818.06078079999</v>
       </c>
       <c r="Q93">
-        <v>88960.8435984</v>
+        <v>87815.56078079999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4817462855919534</v>
+        <v>0.5350404525347351</v>
       </c>
       <c r="T93">
-        <v>8.497404532581839</v>
+        <v>9.536207042677422</v>
       </c>
       <c r="U93">
         <v>0.07580000000000001</v>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>1.594539491254724</v>
+        <v>1.577207540262825</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.09859203620277879</v>
+        <v>0.09864450670228178</v>
       </c>
       <c r="C94">
-        <v>39823.51585360011</v>
+        <v>19887.64263854688</v>
       </c>
       <c r="D94">
-        <v>1714309.4958536</v>
+        <v>1713260.212638547</v>
       </c>
       <c r="E94">
-        <v>1656609.08</v>
+        <v>1675495.67</v>
       </c>
       <c r="F94">
-        <v>1737566.28</v>
+        <v>1756452.87</v>
       </c>
       <c r="G94">
         <v>63080.3</v>
@@ -9001,28 +9001,28 @@
         <v>207730.1</v>
       </c>
       <c r="M94">
-        <v>131707.524024</v>
+        <v>133139.127546</v>
       </c>
       <c r="N94">
-        <v>76022.57597599999</v>
+        <v>74590.97245399997</v>
       </c>
       <c r="O94">
-        <v>15204.5151952</v>
+        <v>14918.1944908</v>
       </c>
       <c r="P94">
-        <v>60818.06078079999</v>
+        <v>59672.77796319998</v>
       </c>
       <c r="Q94">
-        <v>87815.56078079999</v>
+        <v>86670.27796319997</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5350404525347351</v>
+        <v>0.6035615243183116</v>
       </c>
       <c r="T94">
-        <v>9.536207042677422</v>
+        <v>10.87181026994317</v>
       </c>
       <c r="U94">
         <v>0.07580000000000001</v>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>1.577207540262825</v>
+        <v>1.560248319399784</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.09864450670228178</v>
+        <v>0.09869697720178477</v>
       </c>
       <c r="C95">
-        <v>19887.64263854688</v>
+        <v>-46.94688556203619</v>
       </c>
       <c r="D95">
-        <v>1713260.212638547</v>
+        <v>1712212.213114438</v>
       </c>
       <c r="E95">
-        <v>1675495.67</v>
+        <v>1694382.26</v>
       </c>
       <c r="F95">
-        <v>1756452.87</v>
+        <v>1775339.46</v>
       </c>
       <c r="G95">
         <v>63080.3</v>
@@ -9083,28 +9083,28 @@
         <v>207730.1</v>
       </c>
       <c r="M95">
-        <v>133139.127546</v>
+        <v>134570.731068</v>
       </c>
       <c r="N95">
-        <v>74590.97245399997</v>
+        <v>73159.36893199998</v>
       </c>
       <c r="O95">
-        <v>14918.1944908</v>
+        <v>14631.8737864</v>
       </c>
       <c r="P95">
-        <v>59672.77796319998</v>
+        <v>58527.49514559998</v>
       </c>
       <c r="Q95">
-        <v>86670.27796319997</v>
+        <v>85524.99514559998</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6035615243183116</v>
+        <v>0.6949229533630801</v>
       </c>
       <c r="T95">
-        <v>10.87181026994317</v>
+        <v>12.65261457296416</v>
       </c>
       <c r="U95">
         <v>0.07580000000000001</v>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>1.560248319399784</v>
+        <v>1.543649933023191</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.09869697720178477</v>
+        <v>0.09874944770128778</v>
       </c>
       <c r="C96">
-        <v>-46.94688556203619</v>
+        <v>-19980.25507298438</v>
       </c>
       <c r="D96">
-        <v>1712212.213114438</v>
+        <v>1711165.494927016</v>
       </c>
       <c r="E96">
-        <v>1694382.26</v>
+        <v>1713268.85</v>
       </c>
       <c r="F96">
-        <v>1775339.46</v>
+        <v>1794226.05</v>
       </c>
       <c r="G96">
         <v>63080.3</v>
@@ -9165,28 +9165,28 @@
         <v>207730.1</v>
       </c>
       <c r="M96">
-        <v>134570.731068</v>
+        <v>136002.33459</v>
       </c>
       <c r="N96">
-        <v>73159.36893199998</v>
+        <v>71727.76540999999</v>
       </c>
       <c r="O96">
-        <v>14631.8737864</v>
+        <v>14345.553082</v>
       </c>
       <c r="P96">
-        <v>58527.49514559998</v>
+        <v>57382.21232799999</v>
       </c>
       <c r="Q96">
-        <v>85524.99514559998</v>
+        <v>84379.71232799999</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6949229533630801</v>
+        <v>0.8228289540257564</v>
       </c>
       <c r="T96">
-        <v>12.65261457296416</v>
+        <v>15.14574059719356</v>
       </c>
       <c r="U96">
         <v>0.07580000000000001</v>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>1.543649933023191</v>
+        <v>1.527400986359789</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.09874944770128778</v>
+        <v>0.09880191820079076</v>
       </c>
       <c r="C97">
-        <v>-19980.25507298438</v>
+        <v>-39912.28427222325</v>
       </c>
       <c r="D97">
-        <v>1711165.494927016</v>
+        <v>1710120.055727777</v>
       </c>
       <c r="E97">
-        <v>1713268.85</v>
+        <v>1732155.44</v>
       </c>
       <c r="F97">
-        <v>1794226.05</v>
+        <v>1813112.64</v>
       </c>
       <c r="G97">
         <v>63080.3</v>
@@ -9247,28 +9247,28 @@
         <v>207730.1</v>
       </c>
       <c r="M97">
-        <v>136002.33459</v>
+        <v>137433.938112</v>
       </c>
       <c r="N97">
-        <v>71727.76540999999</v>
+        <v>70296.16188799997</v>
       </c>
       <c r="O97">
-        <v>14345.553082</v>
+        <v>14059.2323776</v>
       </c>
       <c r="P97">
-        <v>57382.21232799999</v>
+        <v>56236.92951039998</v>
       </c>
       <c r="Q97">
-        <v>84379.71232799999</v>
+        <v>83234.42951039998</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8228289540257564</v>
+        <v>1.014687955019771</v>
       </c>
       <c r="T97">
-        <v>15.14574059719356</v>
+        <v>18.88542963353766</v>
       </c>
       <c r="U97">
         <v>0.07580000000000001</v>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>1.527400986359789</v>
+        <v>1.511490559418541</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.09880191820079078</v>
+        <v>0.1098735887002938</v>
       </c>
       <c r="C98">
-        <v>-39912.28427222325</v>
+        <v>-254084.3444857909</v>
       </c>
       <c r="D98">
-        <v>1710120.055727777</v>
+        <v>1514834.585514209</v>
       </c>
       <c r="E98">
-        <v>1732155.44</v>
+        <v>1751042.03</v>
       </c>
       <c r="F98">
-        <v>1813112.64</v>
+        <v>1831999.23</v>
       </c>
       <c r="G98">
         <v>63080.3</v>
@@ -9329,45 +9329,45 @@
         <v>207730.1</v>
       </c>
       <c r="M98">
-        <v>137433.938112</v>
+        <v>164879.9307</v>
       </c>
       <c r="N98">
-        <v>70296.161888</v>
+        <v>42850.16930000001</v>
       </c>
       <c r="O98">
-        <v>14059.2323776</v>
+        <v>8570.033860000001</v>
       </c>
       <c r="P98">
-        <v>56236.9295104</v>
+        <v>34280.13544000001</v>
       </c>
       <c r="Q98">
-        <v>83234.4295104</v>
+        <v>61277.63544000001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.014687955019768</v>
+        <v>1.334452956676457</v>
       </c>
       <c r="T98">
-        <v>18.88542963353761</v>
+        <v>25.11824469411108</v>
       </c>
       <c r="U98">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V98">
         <v>0.2</v>
       </c>
       <c r="W98">
-        <v>0.06064000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y98">
-        <v>1.511490559418541</v>
+        <v>1.259887113720142</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1098735887002938</v>
+        <v>0.1342147402875483</v>
       </c>
       <c r="C99">
-        <v>-254084.3444857909</v>
+        <v>-576961.1620824602</v>
       </c>
       <c r="D99">
-        <v>1514834.585514209</v>
+        <v>1210844.35791754</v>
       </c>
       <c r="E99">
-        <v>1751042.03</v>
+        <v>1769928.62</v>
       </c>
       <c r="F99">
-        <v>1831999.23</v>
+        <v>1850885.82</v>
       </c>
       <c r="G99">
         <v>63080.3</v>
@@ -9411,45 +9411,45 @@
         <v>207730.1</v>
       </c>
       <c r="M99">
-        <v>164879.9307</v>
+        <v>219515.058252</v>
       </c>
       <c r="N99">
-        <v>42850.16930000001</v>
+        <v>-11784.95825200001</v>
       </c>
       <c r="O99">
-        <v>8570.033860000001</v>
+        <v>-2356.991650400003</v>
       </c>
       <c r="P99">
-        <v>34280.13544000001</v>
+        <v>-9427.966601600008</v>
       </c>
       <c r="Q99">
-        <v>61277.63544000001</v>
+        <v>17569.53339839999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.334452956676457</v>
+        <v>1.999218464655095</v>
       </c>
       <c r="T99">
-        <v>25.11824469411108</v>
+        <v>38.07576177200405</v>
       </c>
       <c r="U99">
-        <v>0.09</v>
+        <v>0.1186</v>
       </c>
       <c r="V99">
-        <v>0.2</v>
+        <v>0.1892627336403765</v>
       </c>
       <c r="W99">
-        <v>0.07199999999999999</v>
+        <v>0.09615343979025136</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y99">
-        <v>1.259887113720142</v>
+        <v>0.9463136682018822</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1342147402875483</v>
+        <v>0.1349427402875483</v>
       </c>
       <c r="C100">
-        <v>-576961.1620824602</v>
+        <v>-603071.6934882863</v>
       </c>
       <c r="D100">
-        <v>1210844.35791754</v>
+        <v>1203620.416511714</v>
       </c>
       <c r="E100">
-        <v>1769928.62</v>
+        <v>1788815.21</v>
       </c>
       <c r="F100">
-        <v>1850885.82</v>
+        <v>1869772.41</v>
       </c>
       <c r="G100">
         <v>63080.3</v>
@@ -9493,37 +9493,37 @@
         <v>207730.1</v>
       </c>
       <c r="M100">
-        <v>219515.058252</v>
+        <v>221755.007826</v>
       </c>
       <c r="N100">
-        <v>-11784.95825200001</v>
+        <v>-14024.90782600001</v>
       </c>
       <c r="O100">
-        <v>-2356.991650400003</v>
+        <v>-2804.981565200002</v>
       </c>
       <c r="P100">
-        <v>-9427.966601600008</v>
+        <v>-11219.92626080001</v>
       </c>
       <c r="Q100">
-        <v>17569.53339839999</v>
+        <v>15777.57373919999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.999218464655095</v>
+        <v>3.952636929310189</v>
       </c>
       <c r="T100">
-        <v>38.07576177200405</v>
+        <v>76.1515235440081</v>
       </c>
       <c r="U100">
         <v>0.1186</v>
       </c>
       <c r="V100">
-        <v>0.1892627336403765</v>
+        <v>0.1873509888561302</v>
       </c>
       <c r="W100">
-        <v>0.09615343979025136</v>
+        <v>0.09638017272166297</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.9463136682018822</v>
+        <v>0.9367549442806512</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1349427402875483</v>
-      </c>
-      <c r="C101">
-        <v>-603071.6934882863</v>
-      </c>
-      <c r="D101">
-        <v>1203620.416511714</v>
-      </c>
-      <c r="E101">
-        <v>1788815.21</v>
-      </c>
-      <c r="F101">
-        <v>1869772.41</v>
-      </c>
-      <c r="G101">
-        <v>63080.3</v>
-      </c>
-      <c r="H101">
-        <v>1807701.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>234727.6</v>
-      </c>
-      <c r="K101">
-        <v>26997.5</v>
-      </c>
-      <c r="L101">
-        <v>207730.1</v>
-      </c>
-      <c r="M101">
-        <v>221755.007826</v>
-      </c>
-      <c r="N101">
-        <v>-14024.90782600001</v>
-      </c>
-      <c r="O101">
-        <v>-2804.981565200002</v>
-      </c>
-      <c r="P101">
-        <v>-11219.92626080001</v>
-      </c>
-      <c r="Q101">
-        <v>15777.57373919999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.952636929310189</v>
-      </c>
-      <c r="T101">
-        <v>76.1515235440081</v>
-      </c>
-      <c r="U101">
-        <v>0.1186</v>
-      </c>
-      <c r="V101">
-        <v>0.1873509888561302</v>
-      </c>
-      <c r="W101">
-        <v>0.09638017272166297</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Caa/CCC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.9367549442806512</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
